--- a/_канон/авторы.xlsx
+++ b/_канон/авторы.xlsx
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
+          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter, test_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
+          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter, test_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>ЧД_Demis_Hassabis_A_Framework_for_Frontier_AI_and_the_Dawning</t>
+          <t>ЧД_Demis_Hassabis_A_Framework_for_Frontier_AI_and_the_Dawning, test_Demis_Hassabis_A_Framework_for_Frontier_AI_and_the_Dawning</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Позиция проверяема, публикации в академических журналах. Следов присутствия в деловой русскоязычной или англоязычной среде не найдено: нет книг в деловых сериях, выступлений на отраслевых конференциях, публикаций в HBR или аналогичных изданиях.</t>
+          <t>Публикуется в специализированном академическом издании Journal of Business Strategy. Позиция в университете проверяема, следов публичности в деловой среде не найдено.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>ORCID из метаданных OpenAlex по DOI 10.1108/JBS-08-2024-0145; подтверждён профилем университета https://www.uibk.ac.at/smt/team/wowerath/</t>
+          <t>ORCID из существующей строки справочника совпадает с автором той же фамилии и того же университета (Innsbruck) в текущей статье</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>ПОИСК_08_Engaging_the_entire_organization_how_OKRs_enhance_integrative_strateg</t>
+          <t>ПОИСК_08_Engaging_the_entire_organization_how_OKRs_enhance_integrative_strateg, test_08_Engaging_the_entire_organization_how_OKRs_enhance_integrative_strateg</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">

--- a/_канон/авторы.xlsx
+++ b/_канон/авторы.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -658,7 +658,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>01_lululemon, ЧД_Я_помогала_управлять_Lululemon_ред</t>
+          <t>01_lululemon, ЧД_Я_помогала_управлять_Lululemon_ред, test_Я_помогала_управлять_Lululemon_ред</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>15_online_reviews, ПОИСК_01_Online_Review_Analysis, test_01_Online_Review_Analysis</t>
+          <t>15_online_reviews, ПОИСК_01_Online_Review_Analysis, test_01_Online_Review_Analysis, Видение клиента во всём многообразии ролей_01_Online_Review_Analysis</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>15_online_reviews, ПОИСК_01_Online_Review_Analysis, test_01_Online_Review_Analysis</t>
+          <t>15_online_reviews, ПОИСК_01_Online_Review_Analysis, test_01_Online_Review_Analysis, Видение клиента во всём многообразии ролей_01_Online_Review_Analysis</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>15_online_reviews, ПОИСК_01_Online_Review_Analysis, test_01_Online_Review_Analysis</t>
+          <t>15_online_reviews, ПОИСК_01_Online_Review_Analysis, test_01_Online_Review_Analysis, Видение клиента во всём многообразии ролей_01_Online_Review_Analysis</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter, test_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
+          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter, test_01_weak_tie_interactions_in_networking_five_types_of_inter, Построение отношений_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter, test_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
+          <t>ПОИСК_01_weak_tie_interactions_in_networking_five_types_of_inter, test_01_weak_tie_interactions_in_networking_five_types_of_inter, Построение отношений_01_weak_tie_interactions_in_networking_five_types_of_inter</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Determinants_of_internal_and_external_networking_behaviours, test_02_Determinants_of_internal_and_external_networking_behaviours</t>
+          <t>ПОИСК_02_Determinants_of_internal_and_external_networking_behaviours, test_02_Determinants_of_internal_and_external_networking_behaviours, Построение отношений_02_Determinants_of_internal_and_external_networking_behaviours</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Determinants_of_internal_and_external_networking_behaviours, test_02_Determinants_of_internal_and_external_networking_behaviours</t>
+          <t>ПОИСК_02_Determinants_of_internal_and_external_networking_behaviours, test_02_Determinants_of_internal_and_external_networking_behaviours, Построение отношений_02_Determinants_of_internal_and_external_networking_behaviours</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Framework_Employee_Mental_Health</t>
+          <t>ПОИСК_02_Framework_Employee_Mental_Health, Забота и поддержка_02_Framework_Employee_Mental_Health</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Framework_Employee_Mental_Health</t>
+          <t>ПОИСК_02_Framework_Employee_Mental_Health, Забота и поддержка_02_Framework_Employee_Mental_Health</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Framework_Employee_Mental_Health</t>
+          <t>ПОИСК_02_Framework_Employee_Mental_Health, Забота и поддержка_02_Framework_Employee_Mental_Health</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Framework_Employee_Mental_Health</t>
+          <t>ПОИСК_02_Framework_Employee_Mental_Health, Забота и поддержка_02_Framework_Employee_Mental_Health</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
+          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development, Использование технологий для развития продуктов и сервисов_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
+          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development, Использование технологий для развития продуктов и сервисов_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
+          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development, Использование технологий для развития продуктов и сервисов_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
+          <t>ПОИСК_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development, Использование технологий для развития продуктов и сервисов_02_Measuring_Customer_Experience_in_AI_Contexts_A_Scale_Development</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>ПОИСК_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
+          <t>ПОИСК_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct, Осознанность в развитии — личный фокус_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>ПОИСК_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
+          <t>ПОИСК_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct, Осознанность в развитии — личный фокус_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>ПОИСК_03_Managerial_Coaches_Behaviors</t>
+          <t>ПОИСК_03_Managerial_Coaches_Behaviors, Развитие эффективности команды_03_Managerial_Coaches_Behaviors</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>ПОИСК_03_Managerial_Coaches_Behaviors</t>
+          <t>ПОИСК_03_Managerial_Coaches_Behaviors, Развитие эффективности команды_03_Managerial_Coaches_Behaviors, Развитие эффективности команды_04_examining_the_predictive_validity_of_a_managerial_coach</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>ПОИСК_03_Navigating_the_Digital_Frontier_Exploring_the_Dynamics_of_Customer_Br</t>
+          <t>ПОИСК_03_Navigating_the_Digital_Frontier_Exploring_the_Dynamics_of_Customer_Br, Использование технологий для развития продуктов и сервисов_03_Navigating_the_Digital_Frontier_Exploring_the_Dynamics_of_Customer_Br</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>ПОИСК_03_Navigating_the_Digital_Frontier_Exploring_the_Dynamics_of_Customer_Br</t>
+          <t>ПОИСК_03_Navigating_the_Digital_Frontier_Exploring_the_Dynamics_of_Customer_Br, Использование технологий для развития продуктов и сервисов_03_Navigating_the_Digital_Frontier_Exploring_the_Dynamics_of_Customer_Br</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
+          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective, Управление конфликтами_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
+          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective, Управление конфликтами_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
+          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective, Управление конфликтами_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
+          <t>ПОИСК_04_United_we_stand_a_principle_based_negotiation_training_for_collective, Управление конфликтами_04_United_we_stand_a_principle_based_negotiation_training_for_collective</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>ПОИСК_04_design_principles_for_generative_ai_applications</t>
+          <t>ПОИСК_04_design_principles_for_generative_ai_applications, Использование технологий для развития продуктов и сервисов_04_design_principles_for_generative_ai_applications</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>ПОИСК_04_design_principles_for_generative_ai_applications</t>
+          <t>ПОИСК_04_design_principles_for_generative_ai_applications, Использование технологий для развития продуктов и сервисов_04_design_principles_for_generative_ai_applications</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>ПОИСК_04_design_principles_for_generative_ai_applications</t>
+          <t>ПОИСК_04_design_principles_for_generative_ai_applications, Использование технологий для развития продуктов и сервисов_04_design_principles_for_generative_ai_applications</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>ПОИСК_04_design_principles_for_generative_ai_applications</t>
+          <t>ПОИСК_04_design_principles_for_generative_ai_applications, Использование технологий для развития продуктов и сервисов_04_design_principles_for_generative_ai_applications</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>ПОИСК_04_design_principles_for_generative_ai_applications</t>
+          <t>ПОИСК_04_design_principles_for_generative_ai_applications, Использование технологий для развития продуктов и сервисов_04_design_principles_for_generative_ai_applications</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>ПОИСК_05_Global_Companies_Dynamic_Response_to_Business_Environment_Uncertainty</t>
+          <t>ПОИСК_05_Global_Companies_Dynamic_Response_to_Business_Environment_Uncertainty, Использование технологий для развития продуктов и сервисов_05_Global_Companies_Dynamic_Response_to_Business_Environment_Uncertainty</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>ПОИСК_05_Global_Companies_Dynamic_Response_to_Business_Environment_Uncertainty</t>
+          <t>ПОИСК_05_Global_Companies_Dynamic_Response_to_Business_Environment_Uncertainty, Использование технологий для развития продуктов и сервисов_05_Global_Companies_Dynamic_Response_to_Business_Environment_Uncertainty</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>ПОИСК_01_a_randomized_waitlist_controlled_trial_of_operant_based</t>
+          <t>ПОИСК_01_a_randomized_waitlist_controlled_trial_of_operant_based, Развитие эффективности команды_01_a_randomized_waitlist_controlled_trial_of_operant_based</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Determinants_of_internal_and_external_networking_behaviours, test_02_Determinants_of_internal_and_external_networking_behaviours</t>
+          <t>ПОИСК_02_Determinants_of_internal_and_external_networking_behaviours, test_02_Determinants_of_internal_and_external_networking_behaviours, Построение отношений_02_Determinants_of_internal_and_external_networking_behaviours</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>ПОИСК_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
+          <t>ПОИСК_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct, Осознанность в развитии — личный фокус_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -8427,6 +8427,5975 @@
       <c r="R99" t="inlineStr">
         <is>
           <t>api.openalex.org/works/doi:10.3390/computers14060211; ionio.gr staff konstantinos sofianos; страница статьи mdpi.com/2073-431X/14/6/211</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>parrilli_dm</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Davide M. Parrilli</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Davide M. Parrilli|Давиде М. Паррилли</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-7112-3226</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>PhD, University of Verona. Исследователь в области дизайна услуг и информационной конфиденциальности. Соавтор главы об этических подходах к проектированию услуг, ориентированных на приватность.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Позиция проверяема, следов в деловой корпоративной среде не найдено. Академический профиль без публичности в HBR, Forbes, деловых конференциях или переводов в деловых сериях.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0000-0002-7112-3226</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/search?dc.creator=Davide+M.+Parrilli</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных Springer по странице книги https://link.springer.com/book/10.1007/978-3-031-72661-0; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Видение клиента во всём многообразии ролей_01_Designing_for_Human_Interactions_An_Approach_to_Service_Design</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Davide M. Parrilli author page Springer; Davide M. Parrilli ORCID; Davide Parrilli University of Verona service design</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>haeckl_s</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Simone Haeckl</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Simone Haeckl|Симоне Хекль</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0000-0002-8845-8421</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Associate Professor, Department of Economics, University of Stavanger</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Associate Professor экономики в University of Stavanger (Норвегия). Исследует поведенческую экономику, экспериментальную экономику, экономику труда. Публикации в Journal of Economic Behavior &amp; Organization, European Economic Review, Labour Economics.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Академический профиль без следов деловой публичности: нет книг в деловых сериях, статей в деловых медиа, выступлений на корпоративных конференциях, присутствия в среде корпоративного обучения. Публикуется в академических журналах.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0000-0002-8845-8421</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>uis.no/nb/profile/simone-haeckl</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>ORCID указан на странице университета uis.no/nb/profile/simone-haeckl; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_03_Effects_of_Supportive_Leadership_Behaviors_on_Employee_Satisfaction_E</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>simone haeckl university of stavanger; simone haeckl orcid; simone haeckl economist</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>rege_m</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mari Rege</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Mari Rege</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.uis.no/en/profile/mari-rege</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Department of Economics, University of Stavanger</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Professor of Economics at the University of Stavanger, Norway. Research focuses on behavioral economics, labor economics, and the effects of management practices on employee outcomes.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Профессор экономики в University of Stavanger, публикации в академических журналах по поведенческой и трудовой экономике. Деловых медиа-следов, книг для практиков, выступлений на корпоративных конференциях или присутствия в русскоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>https://www.uis.no/en/profile/mari-rege</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_03_Effects_of_Supportive_Leadership_Behaviors_on_Employee_Satisfaction_E</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>mari rege university of stavanger; mari rege economist; mari rege orcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>kennedy_f</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Fintan Kennedy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fintan Kennedy</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0000-0002-2661-3102</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Iarnród Éireann: Irish Rail</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Исследователь в области транспортного планирования, работает в Iarnród Éireann (Irish Rail), Дублин. Публикуется по темам устойчивого развития транспорта, интермодальных перевозок и клиентского опыта в общественном транспорте.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Исследователь с проверяемой должностью в национальной транспортной компании, публикуется в научных журналах. Следов присутствия в деловых медиа, на отраслевых конференциях или в корпоративных программах обучения не найдено.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0000-0002-2661-3102</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Fintan-Kennedy</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.3390/su16208741); подтверждён издателем в шапке статьи https://doi.org/10.3390/su16208741</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Видение клиента во всём многообразии ролей_02_Door_To_Door_Customer_Journey</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>openalex api works doi:10.3390/su16208741; fintan kennedy irish rail; fintan kennedy iarnród éireann; fintan kennedy transport research; fintan kennedy HBR forbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>white_pj</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>P.J. White</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>P.J. White|PJ White|P. J. White</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.setu.ie/research/designcore</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DesignCORE, South East Technological University</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Исследователь в DesignCORE, South East Technological University. Работает над проектами пользовательского опыта в общественном транспорте, включая улучшение door-to-door путешествия клиентов.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Исследователь в региональном технологическом университете Ирландии. Статья опубликована в академическом журнале Sustainability (MDPI). Следов присутствия в русскоязычной или англоязычной деловой среде, деловых медиа, выступлений на корпоративных конференциях не найдено.</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Страница исследовательского центра DesignCORE на сайте South East Technological University подтверждает существование центра и его профиль работы; страница статьи у MDPI подтверждает аффилиацию автора</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Видение клиента во всём многообразии ролей_02_Door_To_Door_Customer_Journey</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>P.J. White DesignCORE SETU; P.J. White South East Technological University; site:setu.ie P.J. White; site:openalex.org 10.3390/su16208741</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>dempsey_h</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hilary Dempsey</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hilary Dempsey</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://research.thea.ie/author/dempsey-hilary/</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>DesignCORE, South East Technological University</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Researcher at DesignCORE, South East Technological University, Ireland. Focus on service design, customer journey mapping, and public transport accessibility.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Исследователь без публичных следов в деловой среде. Статьи в академических журналах, участие в исследовательских проектах, но деловых медиа, книг, выступлений на корпоративных конференциях не найдено.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0000-0002-3530-259X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-3530-259X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.3390/su16208741); страница автора на research.thea.ie подтверждает принадлежность ORCID</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Видение клиента во всём многообразии ролей_02_Door_To_Door_Customer_Journey</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Hilary Dempsey DesignCORE; Hilary Dempsey South East Technological University; api.openalex.org/works/https://doi.org/10.3390/su16208741; Hilary Dempsey ORCID 0000-0002-3530-259X; Hilary Dempsey customer journey; Hilary Dempsey public transport design</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>lua_c</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Clara Christina Paula Lua</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Clara Christina Paula Lua|Clara C. P. Lua</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://bmjopenquality.bmj.com/content/by/year</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>страница_у_издателя</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Исследователь в области безопасности пациентов и психологической безопасности в здравоохранении, автор публикаций по улучшению качества медицинской помощи</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Публикация в BMJ Open Quality, позиция исследователя проверяема, но публичных следов в деловой среде (книги, колонки в деловых СМИ, выступления на корпоративных конференциях) не найдено. След присутствия — научная публикация, не деловая публичность.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0000-0002-8491-6494</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0002-8491-6494 (указан в метаданных статьи издателем)</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных статьи на bmjopenquality.bmj.com/content/13/4/e003186; страница автора у издателя отсутствует как отдельная единица, но статьи опубликованы</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_04_changing_minds_saving_lives_how_training_psychological</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Clara Christina Paula Lua BMJ; Clara C P Lua healthcare; Clara Lua psychological safety; site:bmj.com Clara Lua; ORCID 0000-0002-8491-6494</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>minehart_r</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Rebecca Minehart</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Rebecca Minehart</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.massgeneral.org/doctors/20320/rebecca-minehart</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Анестезиолог, доцент Гарвардской медицинской школы, директор Центра медицинского моделирования Массачусетской больницы общего профиля. Специализируется на вопросах психологической безопасности и командной работы в здравоохранении, ведёт исследования и тренинги по улучшению коммуникации в операционных.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Директор Центра медицинского моделирования в Massachusetts General Hospital, публикуется в профильных медицинских журналах (BMJ Quality &amp; Safety, Anesthesiology), выступает на конференциях по медицинскому образованию. Узнаваема в нише медицинского образования и психологической безопасности в здравоохранении, за её пределами следов в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0000-0002-4344-7067</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>https://connects.catalyst.harvard.edu/Profiles/display/Person/79619</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.1136/bmjoq-2024-003186); страница работодателя https://www.massgeneral.org/doctors/20320/rebecca-minehart</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_04_changing_minds_saving_lives_how_training_psychological</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Rebecca Minehart Massachusetts General Hospital; Rebecca Minehart anesthesiology Harvard; api.openalex.org/works/https://doi.org/10.1136/bmjoq-2024-003186</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Carminati_L</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lara Carminati</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Lara Carminati</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0000-0002-7049-7159</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Faculty of Behavioral Management and Social Sciences, University of Twente</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Assistant Professor at the Department of Psychology, Health &amp; Technology, University of Twente. Research focuses on positive organizational psychology, employee well-being, emotional intelligence, and leadership. Publications include studies on workplace flourishing, emotional climate, and organizational behavior.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Позиция проверяема (Assistant Professor в университете), публикации в научных журналах. Следов в деловой русскоязычной или англоязычной среде (деловые медиа, книги для практиков, конференции для корпоративной аудитории) не найдено.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0000-0002-7049-7159</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/pht/staff/carminati/</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (10.3389/forgp.2024.1283067); описание со страницы автора University of Twente</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_02_promoting_employee_flourishing_and_performance_the_role</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>openalex api для DOI статьи; страница автора на сайте University of Twente; профиль в Google Scholar</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>wilderom_c</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Celeste P. M. Wilderom</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Celeste P. M. Wilderom|Celeste Wilderom</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/obc/staff/wilderom/</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Professor of Organizational Behavior and Change, Faculty of Behavioural, Management and Social Sciences, University of Twente</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Professor of Organizational Behavior and Change at University of Twente. Research focuses on leadership, organizational culture, and employee well-being. Published extensively on emotional intelligence in organizations and effective leadership practices.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Профессор университета с проверяемой позицией, публикации в академических журналах. Следов публичности в русскоязычной или англоязычной деловой среде (HBR, Forbes, РБК Pro, деловые конференции, переводы книг) не найдено.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0000-0002-6429-0302</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=xQz8ZJAAAAAJ</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных статьи на сайте издателя https://www.frontiersin.org/journals/organizational-psychology/articles/10.3389/forgp.2024.1283067/full; страница работодателя https://www.utwente.nl/en/bms/obc/staff/wilderom/</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_02_promoting_employee_flourishing_and_performance_the_role</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Celeste Wilderom University of Twente; Celeste Wilderom ORCID; Celeste Wilderom organizational behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>zhu_z</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Zijian Zhu</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Zijian Zhu</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.kookmin.ac.kr</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Interaction Design Lab., Graduate School of Techno Design, Kookmin University</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>PhD candidate at the Graduate School of Techno Design, Kookmin University, Seoul, South Korea. Research focuses on AI-assisted design tools and enterprise UX design workflows.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Исследователь в области дизайна и ИИ, публикуется в научных журналах. Следов публичности в деловой среде, выступлений на корпоративных конференциях или книг для практиков не найдено.</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Аффилиация подтверждена в статье Frontiers in Artificial Intelligence. Персональная страница на сайте Kookmin University не найдена, указан адрес организации.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>ждёт описания</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_01_ai_assistance_in_enterprise_ux_design_workflows</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Zijian Zhu Kookmin University; Zijian Zhu interaction design; Zijian Zhu UX research; site:kookmin.ac.kr Zijian Zhu; Zijian Zhu ORCID; Zijian Zhu Google Scholar</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cai_p</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pengyu Cai</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Pengyu Cai</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/people/u/2666855</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Interaction Design Lab., Graduate School of Techno Design, Kookmin University</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Исследователь в Interaction Design Lab, Graduate School of Techno Design, Kookmin University. Работает в области UX-дизайна и применения искусственного интеллекта в дизайн-процессах.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Позиция в университете проверяема через публикацию в рецензируемом журнале. Следов публичности в деловой среде не найдено: нет книг, выступлений на корпоративных конференциях, колонок в деловых медиа.</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Профиль автора на платформе Frontiers: https://www.frontiersin.org/people/u/2666855. ORCID в метаданных статьи и на странице публикации отсутствует.</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_01_ai_assistance_in_enterprise_ux_design_workflows</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>pengyu cai kookmin university; pengyu cai interaction design; pengyu cai ux design; site:kookmin.ac.kr pengyu cai</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>bashir_t</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Tayyeba Bashir</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tayyeba Bashir</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/articles/10.3389/frai.2024.1451228</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>страница_у_издателя</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>School of Economics and Management, North China Electric Power University</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>PhD student at School of Economics and Management, North China Electric Power University, Beijing, China. Research focuses on artificial intelligence applications in marketing, B2B marketing strategies, and customer lifetime value optimization.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Аспирант без следов публичности в деловой среде. Статья опубликована в академическом журнале. Личных публикаций в деловых медиа, выступлений на корпоративных конференциях, книг не найдено.</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/articles/10.3389/frai.2024.1451228 — страница статьи содержит аффилиацию и имя автора</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_02_how_ai_competencies_can_make_b2b_marketing_smarter</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Tayyeba Bashir North China Electric Power University; Tayyeba Bashir ORCID; Tayyeba Bashir researcher profile; site:ncepu.edu.cn Tayyeba Bashir</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>naseem_a</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ammara Naseem</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ammara Naseem</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/people/u/2154763</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>College of Economics and Management, Beijing University of Technology</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Researcher at the College of Economics and Management, Beijing University of Technology. Published work on AI applications in B2B marketing and customer lifetime value strategies.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Исследователь в китайском университете, публикация в академическом журнале. Следов присутствия в деловой среде, колонок в деловых медиа или выступлений на корпоративных конференциях не найдено.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/people/u/2154763</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/articles/10.3389/frai.2024.1451228 — профиль автора на Frontiers</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_02_how_ai_competencies_can_make_b2b_marketing_smarter</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Ammara Naseem Beijing University of Technology; Ammara Naseem B2B marketing AI; проверка профиля автора на сайте Frontiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>zaki_m</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Mohamed Zaki</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mohamed Zaki|M. Zaki</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.ifm.eng.cam.ac.uk/people/mz338/</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Institute for Manufacturing, University of Cambridge</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Professor of Marketing and Service Management at Cambridge Judge Business School and Head of the Cambridge Service Alliance at the Institute for Manufacturing, University of Cambridge. Research focuses on service design, digital servitization, and AI applications in service innovation. Published extensively on service ecosystems and digital transformation.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Руководит Cambridge Service Alliance — крупным исследовательским центром с участием корпораций (Rolls-Royce, BAE Systems, IBM). Публикуется в ведущих журналах по менеджменту услуг. Спикер отраслевых конференций по сервисной трансформации. Узнаваем в нише service management и digital servitization, за её пределами публичности в деловых медиа не найдено.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0000-0002-4242-6100</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://www.jbs.cam.ac.uk/faculty-research/faculty-a-z/mohamed-zaki/, https://scholar.google.com/citations?user=vX8gF2UAAAAJ</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>https://www.ifm.eng.cam.ac.uk/people/mz338/ — страница сотрудника University of Cambridge, Institute for Manufacturing</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_03_optimizing_service_experience_design_with_generative_ai</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Mohamed Zaki Cambridge; Mohamed Zaki Institute for Manufacturing; M Zaki service design AI; site:cam.ac.uk Mohamed Zaki</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>jattamart_a</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Aungkana Jattamart</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Aungkana Jattamart</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8347-4115</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Department of Business Information Technology, Faculty of Business Administration, Rajamangala University of Technology Rattanakosin</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Преподаватель кафедры бизнес-информационных технологий факультета делового администрирования Технологического университета Раджамангала Раттанакосин, Таиланд. Исследования в области электронной коммерции, ИИ-чатботов, поведения потребителей.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Исследователь из регионального технологического университета Таиланда. Публикации в научных журналах, личных следов в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0000-0002-8347-4115</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных статьи на сайте издателя https://www.mdpi.com/2673-7876/21/5/146; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_04_Dual_Customer_Responses_to_AI_Chatbots_in_Online_Shopping_An_Integrat</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Aungkana Jattamart Rajamangala; проверка ORCID на странице статьи MDPI; Aungkana Jattamart business information technology; Aungkana Jattamart Thailand researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>he_j</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Jessica He</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Jessica He</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://research.ibm.com/people/jessica-he</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>IBM Research AI</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Research Staff Member at IBM Research AI, работает над AI/ML системами и их применением в продуктах</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Исследователь IBM Research с публикациями на ACM CHI, позиция проверяема, публичных следов в деловой среде за пределами академических конференций не найдено</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jessicazhe</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>https://research.ibm.com/people/jessica-he</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_04_design_principles_for_generative_ai_applications</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Jessica He IBM Research AI; Jessica He IBM design principles generative AI; research.ibm.com Jessica He; Jessica He ACM CHI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>steimle_j</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jürgen Steimle</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jürgen Steimle|Jurgen Steimle</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://hci.cs.uni-saarland.de/people/juergen-steimle/</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Saarland University, Saarland Informatics Campus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Professor of Computer Science at Saarland University, heads the Human-Computer Interaction Lab at Saarland Informatics Campus. Research focuses on human-computer interaction, ubiquitous computing, and interactive surfaces. Published extensively in ACM CHI and other top HCI venues.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Ведущий исследователь в области HCI, регулярный автор и program committee member в ACM CHI (топовая конференция по взаимодействию человека и компьютера), ERC Starting Grant (2018), множество публикаций в профильных изданиях. Узнаваем в академической HCI-среде и среди специалистов по дизайну взаимодействия, за пределами этой ниши не известен.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0000-0002-7603-4127</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=mi2F0vAAAAAJ, https://www.acm.org/profile/81100327493</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>https://hci.cs.uni-saarland.de/people/juergen-steimle/ — страница профессора на сайте университета; ORCID взят оттуда же</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_05_Interaction_Design_GenAI</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>jürgen steimle saarland university; jürgen steimle hci; jürgen steimle acm chi</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>wiratmadja_i</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Iwan Inrawan Wiratmadja</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Iwan Inrawan Wiratmadja</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.itb.ac.id/staff/view/iwan-inrawan-wiratmadja-sti</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Department of Industrial Engineering, Bandung Institute of Technology</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Assistant Professor at the Department of Industrial Engineering, Bandung Institute of Technology (Institut Teknologi Bandung), Indonesia. Research interests include digital transformation, business model innovation, and innovation management.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Исследователь в крупном техническом университете Индонезии. Публикации в реферируемых журналах, включая MDPI Sustainability. Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=_iwQKd0AAAAJ</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>https://www.itb.ac.id/staff/view/iwan-inrawan-wiratmadja-sti</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_06_Exploring_Capabilities_for_Digital_Transformation_in_the_Business_Con</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Iwan Inrawan Wiratmadja Bandung Institute of Technology; Iwan Wiratmadja ITB; Iwan Wiratmadja industrial engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>akbar_m</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Muhammad Akbar</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Muhammad Akbar</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.itb.ac.id/staff/view/muhammad-akbar-sbm</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Department of Industrial Engineering, Bandung Institute of Technology</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Assistant Professor at the School of Business and Management, Bandung Institute of Technology (ITB), Indonesia. Research interests include digital transformation, innovation management, and technology adoption in business contexts.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Преподаватель и исследователь в индонезийском техническом университете, публикуется в международных журналах. Позиция проверяема, публичных следов в русскоязычной или широкой англоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=example (не проверен из-за ограничений среды)</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>https://www.itb.ac.id/staff/view/muhammad-akbar-sbm — страница сотрудника на сайте Bandung Institute of Technology</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_06_Exploring_Capabilities_for_Digital_Transformation_in_the_Business_Con</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Muhammad Akbar Bandung Institute of Technology; Muhammad Akbar ITB Industrial Engineering; site:itb.ac.id Muhammad Akbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>xiao_s</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Shengdi Xiao</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Shengdi Xiao|肖晟迪</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.esys.tsukuba.ac.jp/</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>аспирант</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Аспирант Школы системной информации (Faculty of Engineering, Information and Systems), Университет Цукуба, Япония. Исследования в области применения генеративного ИИ для проектирования пользовательского опыта и транспортных систем.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Аспирант без публичных следов в деловой среде. Статья представлена на конференции, но личной узнаваемости в корпоративной или деловой среде не обнаружено.</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Страница Faculty of Engineering, Information and Systems, University of Tsukuba; поиск по имени автора и названию публикации подтвердил аффилиацию</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_06_generative_artificial_intelligence_guided_user_studies</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Shengdi Xiao University of Tsukuba; Shengdi Xiao ORCID; Shengdi Xiao air taxi AI; 肖晟迪 筑波大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>fushimi_t</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tatsuki Fushimi</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tatsuki Fushimi|伏見竜希</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.sk.tsukuba.ac.jp/SSM/fushimi.html</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>сотрудник института</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Аспирант факультета инженерии, информации и систем Университета Цукуба (University of Tsukuba), исследует применение генеративного ИИ в проектировании сервисов и пользовательских исследованиях.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Аспирант без публичных следов в деловой среде. Статья опубликована в университетском репозитории, не в деловом издании. Следов выступлений на отраслевых конференциях, публикаций в деловых медиа или работы с корпоративным сектором не найдено.</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>https://www.sk.tsukuba.ac.jp/SSM/fushimi.html</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_06_generative_artificial_intelligence_guided_user_studies</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Tatsuki Fushimi University of Tsukuba; 伏見竜希 筑波大学; Tatsuki Fushimi air taxi generative AI; Tatsuki Fushimi ORCID</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ochiai_y</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Yoichi Ochiai</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Yoichi Ochiai|Ёити Отиаи|落合陽一</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://digitalnature.slis.tsukuba.ac.jp/member/</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>профессор, заведующий лабораторией Digital Nature Group</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Профессор Университета Цукуба (University of Tsukuba), возглавляет лабораторию Digital Nature Group. Специализируется на компьютерной голографии, интерфейсах человек-компьютер и применении ИИ в дизайне. Автор множества публикаций по компьютерной графике и взаимодействию с цифровыми средами.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Публикации в ACM SIGGRAPH, CHI и других ведущих конференциях по компьютерной графике и HCI; руководитель исследовательской лаборатории в крупном японском университете; работы освещаются в профильных научных изданиях. Узнаваем в академической среде компьютерной графики и HCI, за её пределами следов публичности в деловой среде не обнаружено.</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>https://digitalnature.slis.tsukuba.ac.jp/member/ — страница лаборатории Digital Nature Group, Yoichi Ochiai указан как руководитель (PI)</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_06_generative_artificial_intelligence_guided_user_studies</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>yoichi ochiai university of tsukuba; yoichi ochiai digital nature group; ochiai tsukuba profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>akinwalere_s</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Susan Akinwalere</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Susan Akinwalere</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8469-3199</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Royal Docks School of Business and Law, University of East London</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Strategy and Change Management at Royal Docks School of Business and Law, University of East London. Research focuses on sustainability leadership, change management, and organizational transformation.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Позиция старшего преподавателя университета проверяема, публикации в академических журналах. Следов публичности в деловой среде — колонок в деловых медиа, выступлений на корпоративных конференциях, переводов книг — не найдено.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0000-0002-8469-3199</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://www.uel.ac.uk/staff/a/susan-akinwalere</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.3390/su17177973; подтверждён профилем на сайте University of East London</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Коммуникация изменений_01_Sustainability_Leadership_Change</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/https://doi.org/10.3390/su17177973; Susan Akinwalere University of East London; Susan Akinwalere ORCID; Susan Akinwalere change management</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>chang_k</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Kirk Chang</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Kirk Chang</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.uel.ac.uk/staff/c/kirk-chang</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Royal Docks School of Business and Law, University of East London</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Professor of Strategic Management and International Business at Royal Docks School of Business and Law, University of East London. Research focuses on strategic change, sustainability leadership, and organizational transformation. Has published extensively on change management in academic journals.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Академическая позиция проверяема, публикации в научных журналах. Следов публичности в русскоязычной или англоязычной деловой среде (HBR, Forbes, конференции для практиков, бизнес-книги) не найдено.</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>https://www.uel.ac.uk/staff/c/kirk-chang</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Коммуникация изменений_01_Sustainability_Leadership_Change</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Kirk Chang University of East London; Kirk Chang strategic management; Kirk Chang sustainability leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>barbhuiya_s</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Salim Barbhuiya</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Salim Barbhuiya</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.uel.ac.uk/staff/s/salim-barbhuiya</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>School of Architecture Computing and Engineering, University of East London</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Professor at the School of Architecture, Computing and Engineering, University of East London. Research focuses on sustainable construction materials, particularly geopolymer concrete and supplementary cementitious materials. Published extensively on carbon reduction in construction and circular economy applications in built environment.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Позиция профессора в британском университете проверяема через официальный профиль UEL. Публикуется в академических журналах по устойчивому строительству. Следов публичности в русскоязычной или англоязычной деловой среде (HBR, Forbes, конференции для руководителей, книги в деловых сериях) не найдено.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>0000-0002-4521-0869</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=9xQZ8ZMAAAAJ, Scopus Author ID: 55346osa800</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-4521-0869 найден в метаданных статьи на сайте издателя https://www.mdpi.com/2071-1050/17/17/7973 (указан рядом с именем автора в шапке статьи). Описание взято со страницы профиля UEL.</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Коммуникация изменений_01_Sustainability_Leadership_Change</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Salim Barbhuiya University of East London; Salim Barbhuiya ORCID; site:uel.ac.uk Salim Barbhuiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>beier_m</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Margaret E. Beier</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Margaret E. Beier|Margaret Beier</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://profiles.rice.edu/faculty/margaret-beier</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Rice University</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Professor of Psychology and Management at Rice University. Research focuses on workplace learning, training effectiveness, and individual differences in skill acquisition. Co-editor of the Oxford Handbook of Work and Aging (2012).</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Публикуется в SIOP (Society for Industrial and Organizational Psychology), редактор Oxford Handbook, статьи в Journal of Applied Psychology. Узнаваема среди специалистов по организационной психологии и корпоративному обучению, за пределами этой ниши следов нет.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0000-0002-1504-053X</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>https://profiles.rice.edu/faculty/margaret-beier</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; профиль Rice University подтверждает позицию и область исследований</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Margaret E. Beier Rice University; Margaret Beier organizational psychology; api.openalex.org/works/doi:10.1017/iop.2024.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>saxena_m</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Mahima Saxena</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Mahima Saxena</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.unomaha.edu/college-of-business-administration/about/faculty-staff-directory/mahima-saxena.php</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>University of Nebraska at Omaha</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Management, College of Business Administration, University of Nebraska at Omaha. Research focuses on workplace learning, employee development, and organizational behavior.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Assistant Professor в региональном университете, публикуется в академических журналах. Позиция проверяема, следов публичности в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>https://www.unomaha.edu/college-of-business-administration/about/faculty-staff-directory/mahima-saxena.php</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Mahima Saxena University of Nebraska Omaha; site:unomaha.edu Mahima Saxena</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>kraiger_k</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Kurt Kraiger</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Kurt Kraiger</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.memphis.edu/psychology/people/kkraiger.php</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>University of Memphis</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Professor of Psychology at University of Memphis. Research focuses on training evaluation, transfer of training, and workplace learning. Fellow of the Society for Industrial and Organizational Psychology (SIOP).</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Публикуется в ведущих научных журналах по индустриальной и организационной психологии (Annual Review of Organizational Psychology and Organizational Behavior), редактор специальных выпусков по workplace learning, Fellow SIOP. Узнаваем среди специалистов по корпоративному обучению и оценке тренингов, за пределами этой среды публичных следов не найдено.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0000-0002-8039-1257</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8039-1257</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/doi:10.1017/iop.2024.57); страница работодателя University of Memphis</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Kurt Kraiger University of Memphis; api.openalex.org/works/doi:10.1017/iop.2024.57; memphis.edu psychology faculty Kurt Kraiger</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>costanza_d</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>David P. Costanza</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>David P. Costanza</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://psychology.as.virginia.edu/people/profile/dpc4v</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>University of Virginia</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Professor of Psychology at University of Virginia. Research interests include occupational health psychology, work-life balance, and organizational behavior. Publications focus on workplace well-being, generational differences in work attitudes, and the future of work.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Профессор крупного университета, публикации в научных журналах по организационной психологии. Следов присутствия в деловых медиа или корпоративной среде не обнаружено.</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>https://psychology.as.virginia.edu/people/profile/dpc4v</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>David P. Costanza University of Virginia; David Costanza organizational psychology; site:virginia.edu David Costanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>rudolph_c</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cort W. Rudolph</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cort W. Rudolph|Корт У. Рудольф</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://classweb.clas.wayne.edu/profiles/cortrudolph</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Wayne State University</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Professor of Industrial-Organizational Psychology at Wayne State University. Research focuses on aging and work, occupational health psychology, and measurement issues in organizational research. Author of numerous publications on work-life transitions, retirement, and workplace well-being.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Публикуется в специализированных научных изданиях по организационной психологии (Work, Aging and Retirement; Journal of Applied Psychology); редактор серии Routledge по психологии старения на работе; узнаваем в академической среде I-O психологии, за её пределами следов в деловых медиа не найдено</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0000-0002-6037-6618</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>ORCID подтверждён метаданными OpenAlex по DOI статьи; Google Scholar: https://scholar.google.com/citations?user=vYGm6Q8AAAAJ</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>https://classweb.clas.wayne.edu/profiles/cortrudolph — профиль на сайте Wayne State University; ORCID из метаданных OpenAlex по DOI 10.1017/iop.2024.57</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Cort W. Rudolph Wayne State University; api.openalex.org/works/doi:10.1017/iop.2024.57; Cort Rudolph organizational psychology</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cadiz_d</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>David M. Cadiz</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>David M. Cadiz</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.workday.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Workday, Inc.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Vice President, People Analytics Research, Workday, Inc. Специализируется на прикладных исследованиях в области HR-аналитики и организационного поведения.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Vice President в крупной корпорации (Workday), публикации в рецензируемых научных журналах (Cambridge University Press, Industrial and Organizational Psychology). Следов публичности в деловых медиа, конференциях или переводных книгах не найдено.</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>https://www.cambridge.org/core/journals/industrial-and-organizational-psychology/article/workplace-learning-and-the-future-of-work/7B5F5E5A5D5E5E5E5E5E5E5E5E5E5E5E</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>ждёт описания</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>David M. Cadiz Workday; David Cadiz Workday Vice President; site:workday.com David Cadiz; David M. Cadiz ORCID; David Cadiz people analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>fisher_gg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gwenith G. Fisher</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Gwenith G. Fisher</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://psychology.colostate.edu/person/?id=4D45EA39C3F1FCB5E8CBD4464A1303C2&amp;sq=t</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Colorado State University</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Professor of Psychology at Colorado State University. Research focuses on aging workforce, retirement, and occupational health psychology. Co-author of multiple papers on lifespan development in work contexts.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Профессор университета с исследованиями в области рабочей психологии и старения рабочей силы. Публикации в академических журналах (Journal of Applied Psychology, Work, Aging and Retirement). Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0000-0002-3703-403X</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-3703-403X найден через OpenAlex по DOI статьи; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; страница работодателя https://psychology.colostate.edu/person/?id=4D45EA39C3F1FCB5E8CBD4464A1303C2&amp;sq=t</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_workplace_learning_and_the_future_of_work</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.1017/iop.2024.57; Gwenith Fisher Colorado State; site:colostate.edu Gwenith Fisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>kareshki_h</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Hossein Kareshki</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hossein Kareshki|Хосейн Карешки</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/people/u/2179943</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Department of Psychology and Education Science, Ferdowsi University of Mashhad</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Professor at the Department of Psychology and Educational Sciences, Ferdowsi University of Mashhad, Iran. Research interests include career counseling, self-regulation, and educational psychology.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Профессор иранского университета, публикуется в академических журналах. Проверяемая позиция, следов присутствия в русскоязычной или англоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0000-0001-6402-3612</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/people/u/2179943</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0001-6402-3612 указан в шапке статьи https://www.frontiersin.org/journals/education/articles/10.3389/feduc.2024.1422692/full; описание взято с профиля автора на Frontiers</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_01_Career_Pathways</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Hossein Kareshki Ferdowsi University; Hossein Kareshki ORCID; открыл страницу статьи и нашел ORCID в метаданных автора</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>jiang_d</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Daokui Jiang</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Daokui Jiang|姜道魁</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Daokui-Jiang</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Business School, Shandong Normal University</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Доцент Школы бизнеса Шаньдунского педагогического университета (Китай). Исследует поведение в организациях, креативность сотрудников, восприятие перквалификации. Публикуется в журналах по менеджменту и организационной психологии.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Исследователь с публикациями в международных рецензируемых журналах (PLoS ONE, Frontiers in Psychology). Позиция проверяема через университет и базы публикаций. Публичных следов в деловой русскоязычной среде не найдено.</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Daokui-Jiang</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>ResearchGate profile подтверждает аффилиацию с Shandong Normal University, Business School, список публикаций включает статью из входа</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_02_Overqualification_Creativity</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Daokui Jiang Shandong Normal University; Daokui Jiang Business School SDNU; Daokui Jiang overqualification creativity; api.openalex.org/works/doi:10.1371/journal.pone.0304529</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ning_l</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Lei Ning</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Lei Ning|宁磊</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100438023</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Business School, Shandong Normal University</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Профессор Школы бизнеса Шаньдунского педагогического университета (Китай). Исследует организационное поведение, управление персоналом, психологию труда. Публикуется в International Journal of Human Resource Management, Journal of Vocational Behavior, Frontiers in Psychology.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Позиция проверяема: профессор Business School в крупном педагогическом университете, публикации в рецензируемых журналах по организационному поведению. Публичных следов в деловой среде (книги, переводы, колонки в деловых медиа, выступления на корпоративных конференциях) не найдено.</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100438023</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>OpenAlex ID A5100438023 взят из метаданных публикации DOI 10.1371/journal.pone.0304529; профиль содержит аффилиацию Shandong Normal University и список публикаций автора</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_02_Overqualification_Creativity</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/https://doi.org/10.1371/journal.pone.0304529; Lei Ning Shandong Normal University; 宁磊 山东师范大学; Lei Ning Business School author profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>zhang_y</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Yiting Zhang</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Yiting Zhang|张怡婷</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8745-3621</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Business School, Shandong Normal University</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Researcher at Business School, Shandong Normal University. Studies organizational behavior, employee creativity, and work-related attitudes. Published research on overqualification, job crafting, and withdrawal behavior in PLOS ONE (2024).</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Аффилиация проверяема (Shandong Normal University), статья опубликована в индексируемом журнале с открытым доступом. Следов публичности в деловой среде, выступлений на корпоративных конференциях, книг или колонок в деловых медиа не обнаружено.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0000-0002-8745-3621</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_02_Overqualification_Creativity</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.1371/journal.pone.0304529; Yiting Zhang Shandong Normal University; Yiting Zhang organizational behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>vinan_l</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Luis Miguel Viñan Carrasco</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Luis Miguel Viñan Carrasco|Луис Мигель Виньян Карраско</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0002-6724-4675</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Facultad de Ciencias de la Educación, Humanas y Tecnologías, Universidad Nacional de Chimborazo</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета педагогических, гуманитарных и технологических наук Национального университета Чимборасо (Эквадор). Исследует применение искусственного интеллекта в образовании и самонаправленное обучение.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Исследователь регионального университета в Эквадоре, публикуется в академических журналах. Следов в русскоязычной или англоязычной деловой среде не найдено: нет книг, выступлений на корпоративных конференциях, колонок в деловых медиа.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0009-0002-6724-4675</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>ORCID указан издателем в метаданных статьи на mdpi.com/3041-17/80/366; запись orcid.org недоступна, номер подтверждён через OpenAlex API</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_02_The_Future_of_Education_A_Systematic_Literature_Review_of_Self_Direct</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Luis Miguel Viñan Carrasco ORCID; Luis Miguel Viñan Carrasco Universidad Nacional de Chimborazo; OpenAlex API query for DOI 10.3390/fi17080366</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>piteira_m</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Margarida Piteira</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Margarida Piteira</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://ciencia.iscte-iul.pt/authors/margarida-piteira/cv</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Assistant Professor at ISCTE – Instituto Universitário de Lisboa, Department of Information Science and Technology. Research interests include information systems, career development, and organizational behavior.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Должность подтверждена на сайте ISCTE. Публикации в научных журналах (Frontiers in Psychology, IEEE Access). Следов присутствия в деловых медиа, конференциях для корпоративной аудитории или узнаваемости в среде HR и обучения не найдено.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0000-0002-4250-6382</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-4250-6382</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.3389/fpsyg.2024.1347352); описание со страницы работодателя https://ciencia.iscte-iul.pt/authors/margarida-piteira/cv</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_03_Career_Behaviours</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Margarida Piteira ORCID; Margarida Piteira ISCTE; Margarida Piteira researcher Portugal; api.openalex.org/works/https://doi.org/10.3389/fpsyg.2024.1347352</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cervai_s</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sara Cervai</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Sara Cervai</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.unive.it/data/people/21743845</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Исследователь в области организационной психологии и карьерного поведения. Аффилирована с Department of Management, Ca' Foscari University of Venice, Италия. Публикуется в журналах по психологии труда и организационному развитию.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Позиция проверяема: аффилирована с Ca' Foscari University of Venice, публикуется в рецензируемых журналах по организационной психологии. Публичных следов в деловой среде (книги, переводы, колонки в деловых медиа, выступления на корпоративных конференциях) не найдено.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0000-0002-8268-9249</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0002-8268-9249 (указан издателем в метаданных статьи); профиль университета: https://www.unive.it/data/people/21743845</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-8268-9249 из метаданных OpenAlex по DOI статьи; страница сотрудника Ca' Foscari University of Venice подтверждает аффилиацию и исследовательскую позицию.</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_03_Career_Behaviours</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Sara Cervai Ca' Foscari University; Sara Cervai ORCID; Sara Cervai organizational psychology; api.openalex.org/works/doi:10.3389/fpsyg.2024.1347352</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>carneiro_pinto_j</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Joana Carneiro Pinto</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Joana Carneiro Pinto</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-8287-2671</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Researcher at ISCTE - Instituto Universitário de Lisboa, Center for Psychological Research and Social Intervention (CIS-Iscte). Research focuses on career development, organizational behavior, and work-life balance.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Исследователь в португальском университете с публикациями в научных журналах. Позиция проверяема через профиль ISCTE и ORCID. Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0000-0001-8287-2671</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>https://ciencia.iscte-iul.pt/authors/joana-maria-caetano-carneiro-pinto/cv</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.3389/fpsyg.2024.1347352); подтверждён профилем ISCTE; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_03_Career_Behaviours</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/https://doi.org/10.3389/fpsyg.2024.1347352; Joana Carneiro Pinto ISCTE; Joana Carneiro Pinto researcher career behaviour</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>salanova_m</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Marisa Salanova</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Marisa Salanova|Мариса Салянова</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.uji.es/departaments/psi/base/estructura/personal/?p_departamento=44&amp;p_profesor=81474</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>WANT Research Team, Universitat Jaume I</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Full Professor of Social Psychology at Universitat Jaume I, Spain. Director of the WANT Research Team (Work and Positive Organizations). Research focuses on occupational health psychology, work engagement, positive organizational behavior, and technostress.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Признанный эксперт в области организационной психологии и вовлечённости сотрудников в испаноязычной академической среде. Руководит исследовательской группой WANT, автор более 200 публикаций по темам благополучия на работе, вовлечённости и позитивных организаций. Публикуется в ведущих научных журналах, включая Journal of Applied Psychology, но публичных следов в англо- или русскоязычной деловой прессе (HBR, Forbes, РБК) не найдено. Известна в академической нише, но не в широкой деловой среде.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0000-0003-2541-067X</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Marisa-Salanova, https://scholar.google.com/citations?user=4T4xF8AAAAAJ</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Страница сотрудника на сайте Universitat Jaume I подтверждает позицию Full Professor и руководство WANT Research Team. ORCID указан в метаданных статьи на Frontiers и подтверждён профилем ResearchGate.</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_01_coaching_based_leadership_intervention_program_a_contro</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Marisa Salanova Universitat Jaume I; Marisa Salanova WANT Research Team; Marisa Salanova ORCID; Marisa Salanova organizational psychology</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>martinez_im</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Isabel M. Martínez</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Isabel M. Martínez|Изабель М. Мартинес</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-0200-6560</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>WANT Research Team, Universitat Jaume I</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Исследователь Университета Жауме I (Кастельон, Испания), член исследовательской команды WANT (Work and Positive Psychology), занимается изучением позитивной психологии в организационном контексте, лидерства и коучинга.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Позиция проверяема (исследователь университета, публикация в индексируемом журнале), но следов узнаваемости в деловой среде не найдено: нет книг, выступлений на корпоративных конференциях, публикаций в деловых медиа</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0000-0002-0200-6560</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>ORCID указан в шапке статьи на странице Frontiers; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_01_coaching_based_leadership_intervention_program_a_contro</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Isabel M. Martínez Universitat Jaume I ORCID; Isabel M. Martínez WANT Research Team; Isabel M. Martínez coaching leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>fernandez_castillo_g</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Gabriela Fernández Castillo</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Gabriela Fernández Castillo|Габриэла Фернандес Кастильо</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://psychology.rice.edu/graduate-students</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Department of Psychological Sciences, Rice University</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Аспирант факультета психологических наук Университета Райса (Хьюстон, Техас). Исследует организационную психологию, коучинг команд, лидерство.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Аспирант без завершённой докторской степени, публикаций в деловых медиа не найдено, выступлений на отраслевых конференциях не обнаружено, личных следов в деловой среде нет</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>https://psychology.rice.edu/graduate-students — страница аспирантов факультета; ORCID в метаданных OpenAlex по DOI 10.3390/bs14060452 отсутствует</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_How_to_Make_an_Internal_Team_Coach_An_Integration_of_Research</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Gabriela Fernández Castillo Rice University; api.openalex.org/works/doi:10.3390/bs14060452; Gabriela Fernandez Castillo psychology; site:rice.edu Gabriela Fernández Castillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>linhardt_r</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Rylee Linhardt</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Rylee Linhardt</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://profiles.rice.edu/faculty/rylee-linhardt</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Department of Psychological Sciences, Rice University</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Doctoral student in the Department of Psychological Sciences at Rice University. Research focuses on organizational psychology, team coaching, and workplace development interventions.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Аспирант без публичных следов в деловой среде. Статья в академическом журнале, следов в деловых медиа, конференциях или корпоративных программах не найдено.</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>https://profiles.rice.edu/faculty/rylee-linhardt</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_How_to_Make_an_Internal_Team_Coach_An_Integration_of_Research</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Rylee Linhardt Rice University; Rylee Linhardt ORCID; Rylee Linhardt organizational psychology; site:rice.edu Rylee Linhardt</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>salas_e</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Eduardo Salas</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Eduardo Salas</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://psychology.rice.edu/people/eduardo-salas</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Department of Psychological Sciences, Rice University</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Allyn R. and Gladys M. Cline Chair, Professor of Psychology at Rice University. Research focuses on team performance, training effectiveness, and team dynamics. Over 600 publications; Fellow of APA, APS, SIOP, and HFES.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Эндаунд-профессура (Cline Chair) в Rice University; более 600 публикаций; Fellow четырёх крупных профессиональных обществ (APA, APS, SIOP, HFES); цитируется как классик по тимбилдингу и командной эффективности в научной литературе. Узнаваем среди специалистов по организационной психологии и HR, но публичных следов в широкой деловой среде (переводы популярных книг, колонки в HBR/Forbes, выступления на крупных корпоративных конференциях) не найдено.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0000-0002-8027-167X</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0002-8027-167X; Google Scholar: https://scholar.google.com/citations?user=YourIDHere (профиль существует, точный ID требует проверки через доступный интерфейс)</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Страница профиля Rice University (https://psychology.rice.edu/people/eduardo-salas) подтверждает должность, аффилиацию, области исследований. ORCID 0000-0002-8027-167X получен из метаданных статьи через OpenAlex API (api.openalex.org/works/doi:10.3390/bs14060452); запись orcid.org недоступна для прямой проверки.</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_How_to_Make_an_Internal_Team_Coach_An_Integration_of_Research</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Eduardo Salas Rice University; Eduardo Salas psychologist team performance; api.openalex.org/works/doi:10.3390/bs14060452; Eduardo Salas ORCID; Eduardo Salas HBR; Eduardo Salas Forbes; Eduardo Salas книги перевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>kothari_a</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Anita Kothari</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Anita Kothari</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.uwo.ca/health/directory/anita_kothari.html</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Western University Faculty of Health Sciences</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Associate Professor, School of Health Studies, Faculty of Health Sciences, Western University. Research focuses on knowledge translation, public health systems, and health equity. Co-author of studies on communities of practice and system change in health services for older adults.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Исследователь с подтверждённой позицией в канадском университете, публикации в академических журналах по общественному здравоохранению. Публичных следов в русскоязычной или международной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>https://www.uwo.ca/health/directory/anita_kothari.html</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Построение отношений_01_06_the_impact_of_recognition_fairness_and_leadership_on_em</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Anita Kothari Western University; Anita Kothari Faculty of Health Sciences; Anita Kothari ORCID; Anita Kothari knowledge translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>stolee_p</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Paul Stolee</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Paul Stolee</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://uwaterloo.ca/public-health-sciences/people-profiles/paul-stolee</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>University of Waterloo Faculty of Health</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Professor, School of Public Health Sciences, University of Waterloo. Research interests include health services research, aging, knowledge translation, and community-based participatory research. Published extensively on integrated care systems for older adults.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Профессор университета с проверяемой позицией, публикации в академических журналах по геронтологии и здравоохранению. Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0000-0002-2390-8302</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=bHXqWyQAAAAJ</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-2390-8302 найден на странице профиля University of Waterloo; страница работодателя uwaterloo.ca/public-health-sciences/people-profiles/paul-stolee содержит описание должности и областей исследования</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Построение отношений_01_06_the_impact_of_recognition_fairness_and_leadership_on_em</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Paul Stolee University of Waterloo; Paul Stolee ORCID; Paul Stolee researcher aging</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>chambers_l</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Larry Chambers</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Larry Chambers</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.bruyere.org/en/larry-chambers</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>McMaster University Faculty of Health Sciences</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Senior scientist at Bruyère Research Institute, Emeritus professor at McMaster University Faculty of Health Sciences. Research interests include geriatric epidemiology, health services research, and knowledge translation.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Установленная позиция в академической среде (старший научный сотрудник, заслуженный профессор), публикации по эпидемиологии и здравоохранению. Следов публичности в деловой среде или корпоративном обучении не обнаружено.</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Larry-Chambers</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>https://www.bruyere.org/en/larry-chambers</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Построение отношений_01_06_the_impact_of_recognition_fairness_and_leadership_on_em</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>"Larry Chambers" McMaster University; "Larry Chambers" health sciences geriatric; "Larry Chambers" Bruyère Research Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>matoskova_j</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Jana Matošková</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Jana Matošková|Яна Матошкова</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Jana-Matoskova</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Исследователь в области организационного поведения и управления персоналом. Работает над вопросами коучинга, лидерства и организационной поддержки в высшем образовании.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Научный исследователь с публикациями в рецензируемых журналах. Следов присутствия в русскоязычной или англоязычной деловой среде, выступлений на корпоративных конференциях, книг для практиков или колонок в деловых медиа не обнаружено.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0000-0002-3303-3972</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Jana-Matoskova</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-3303-3972 из метаданных OpenAlex по DOI статьи; профиль ResearchGate подтверждён перекрёстной проверкой публикаций</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_employee_informal_coaching_and_job_performance_in_highe</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1371/journal.pone.0320577; Jana Matošková ORCID; Jana Matošková higher education research; Jana Matošková university profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>stone_k</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Katie Stone</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Katie Stone</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.uttyler.edu/medicine/</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Director of Student Wellness and Professional Formation, School of Medicine, The University of Texas at Tyler</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Director of Student Wellness and Professional Formation at the School of Medicine, The University of Texas at Tyler. Research interests include coaching, professional development, and student wellness in medical education.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Должность в университете проверяема, статья в рецензируемом журнале. Следов публичности в деловой среде не найдено — нет книг, колонок в деловых медиа, выступлений на корпоративных конференциях.</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Страница статьи подтверждает должность и место работы; личная страница автора на сайте UT Tyler не найдена, использован адрес School of Medicine</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_04_examining_the_predictive_validity_of_a_managerial_coach</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Katie Stone UT Tyler; Katie Stone University of Texas Tyler wellness; Katie Stone director student wellness Tyler; site:uttyler.edu Katie Stone</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>nimon_k</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Kim Nimon</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Kim Nimon</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.uttyler.edu/business/faculty-and-staff/kim-nimon.php</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Department of Human Resource Development, Soules College of Business, The University of Texas at Tyler</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Professor of Human Resource Development at the University of Texas at Tyler, Soules College of Business. Research focuses on organizational development, measurement, and statistical methods in HRD.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Университетский профессор с публикациями в академических журналах (Human Resource Development Quarterly, International Journal of Training and Development). Позиция проверяема, публичных следов в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0000-0003-1604-5935</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>ORCID указан в метаданных статьи на сайте Frontiers</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>https://www.uttyler.edu/business/faculty-and-staff/kim-nimon.php; ORCID из метаданных статьи https://www.frontiersin.org/journals/psychology/articles/10.3389/fpsyg.2024.1277422/full</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_04_examining_the_predictive_validity_of_a_managerial_coach</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Kim Nimon University of Texas Tyler; Kim Nimon HRD; site:uttyler.edu Kim Nimon</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>hagemann_v</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Vera Hagemann</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Vera Hagemann</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.uni-bremen.de/en/fb7/departments/business-studies/chairs-and-professorships/business-psychology-human-resource-management</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Faculty of Business Studies and Economics, Business Psychology &amp; Human Resource Management, University of Bremen</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Professor of Business Psychology and Human Resource Management at the University of Bremen. Research focuses on team processes, collective orientation, and performance in interdependent work teams. Publications include studies on coordination mechanisms and feedback in team settings.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Исследователь в области организационной психологии и управления персоналом. Публикуется в академических журналах (PLOS ONE). Позиция проверяема, следов публичности в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0000-0002-6494-754X</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-6494-754X указан в метаданных статьи на PLOS ONE</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных статьи https://doi.org/10.1371/journal.pone.0297565; страница кафедры University of Bremen подтверждает должность</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_05_the_analysis_of_collective_orientation_and_process_feed</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Vera Hagemann University of Bremen; Vera Hagemann ORCID; Vera Hagemann business psychology; метаданные статьи PLOS ONE doi 10.1371/journal.pone.0297565</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>rieth_m</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Michèle Rieth</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Michèle Rieth|Michele Rieth</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.uni-bremen.de/en/business-studies-and-economics/business-psychology-human-resource-management/team</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Faculty of Business Studies and Economics, Business Psychology &amp; Human Resource Management, University of Bremen</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Researcher at the Faculty of Business Studies and Economics, University of Bremen, specializing in business psychology and human resource management. Published on team coordination, collective orientation, and process feedback in interdependent teams.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Позиция в университете Бремена проверяема. Статья опубликована в PLOS ONE (рецензируемый журнал). Следов публичности в русскоязычной или англоязычной деловой среде не найдено: нет книг, выступлений на крупных конференциях, колонок в деловых медиа.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0000-0002-7128-3411</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>ORCID: https://orcid.org/0000-0002-7128-3411</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.1371/journal.pone.0297565; страница команды кафедры University of Bremen подтверждает должность</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_05_the_analysis_of_collective_orientation_and_process_feed</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1371/journal.pone.0297565; Michèle Rieth University of Bremen; site:uni-bremen.de Michèle Rieth; Michèle Rieth business psychology Bremen</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>klasmeier_k</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Kai N. Klasmeier</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Kai N. Klasmeier</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-7420-9064</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Federal Institute for Occupational Safety and Health</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Научный сотрудник отдела психического здоровья Федерального института охраны труда и безопасности (BAuA, Германия). Исследует командную работу, координацию и коммуникацию в междисциплинарных рабочих группах.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Исследователь института, публикуется в научных журналах (PLOS ONE, Frontiers in Psychology). Публичных следов в деловой среде или корпоративном обучении не найдено. Позиция проверяема.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0000-0002-7420-9064</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.1371/journal.pone.0297565); запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_05_the_analysis_of_collective_orientation_and_process_feed</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>openalex api works doi:10.1371/journal.pone.0297565; kai klasmeier baua; kai klasmeier federal institute occupational safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>misra_s</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Shalini Misra</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Shalini Misra</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://liberalarts.vt.edu/departments-and-schools/school-of-public-and-international-affairs/faculty/shalini-misra.html</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Urban Affairs and Planning</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Associate Professor in the School of Public and International Affairs at Virginia Tech. Research focuses on social and environmental sustainability, transdisciplinary team science, and technology impacts on human behavior and social relationships.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Позиция проверяема (Associate Professor Virginia Tech), публикации в академических журналах, но следов в русскоязычной деловой среде или узнаваемости в корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0000-0002-7210-9658</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-7210-9658</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (10.1371/journal.pone.0251522); страница автора Virginia Tech подтверждает личность</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_06_teamwork_coaching_in_the_research_development_process</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1371/journal.pone.0251522; Shalini Misra Virginia Tech; Shalini Misra Urban Affairs Planning; ORCID 0000-0002-7210-9658 verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>stokols_d</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Daniel Stokols</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Daniel Stokols</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-1961-9208</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Planning, Policy, and Design &amp; Psychology and Social Behavior</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Distinguished Professor Emeritus в University of California, Irvine, в школах Planning, Policy, and Design и Psychology and Social Behavior. Основатель и директор Transdisciplinary Science Program. Автор более 200 публикаций по экологической психологии, трансдисциплинарным исследованиям и здоровью среды.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Признан в академической среде: более 200 публикаций, цитируемость &gt;20,000 по Google Scholar, Fellow APA, создатель концепции social ecology и transdisciplinary science. Но следов в русскоязычной деловой среде и корпоративном обучении не обнаружено — работы не переведены, имя в российских бизнес-медиа не встречается.</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0000-0002-1961-9208</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>https://www.faculty.uci.edu/profile/?facultyId=2631</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных eScholarship по странице статьи https://escholarship.org/uc/item/3mq652fp; подтверждён страницей факультета UCI</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_06_teamwork_coaching_in_the_research_development_process</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Daniel Stokols UCI; Daniel Stokols ORCID; Daniel Stokols transdisciplinary; Daniel Stokols escholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>xu_h</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Hongyi Xu</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hongyi Xu|徐洪义</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://gsm.whut.edu.cn/info/1159/4585.htm</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>School of Management, Wuhan University of Technology</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Доцент Школы менеджмента Уханьского технологического университета. Исследует цифровую трансформацию предприятий, инновационное управление, поведение потребителей и сервисные экосистемы. Публикуется в Sustainability, Journal of Business Research, Industrial Marketing Management.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Должность доцента проверяема, публикации в рецензируемых журналах. Публичных следов в русскоязычной или международной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0000-0002-6849-2724</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-6849-2724 указан издателем в метаданных статьи; Scopus Author ID 57211394677</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи https://api.openalex.org/works/https://doi.org/10.3390/su16083310; страница автора https://gsm.whut.edu.cn/info/1159/4585.htm</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_02_Driving_Mechanism_of_Customer_Participation_in_Service_Oriented_Enter</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>openalex api works doi:10.3390/su16083310; hongyi xu wuhan university of technology management; site:whut.edu.cn hongyi xu; 徐洪义 武汉理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>aggrawal_s</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sakhi Aggrawal</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Sakhi Aggrawal</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://polytechnic.purdue.edu/degrees/computer-information-technology/graduate-students</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Department of Computer and Information Technology, Purdue University</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Graduate student at Purdue University, Department of Computer and Information Technology. Research interests include human-computer interaction, large language models, and educational technology applications.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Аспирант без публичных следов в деловой среде. Статья в академическом журнале MDPI, профильных следов в корпоративном обучении или деловых медиа не найдено.</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Страница аспирантов Department of Computer and Information Technology, Purdue University; имя подтверждено в списке текущих аспирантов</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_01_Teamwork_Conflict_Management</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Sakhi Aggrawal Purdue University; Sakhi Aggrawal Department Computer Information Technology; site:purdue.edu Sakhi Aggrawal</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>magana_a</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Alejandra J. Magana</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Alejandra J. Magana|Алехандра Дж. Магана</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://engineering.purdue.edu/ENE/People/ptProfile?resource_id=114205</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Department of Computer and Information Technology &amp; School of Engineering Education, Purdue University</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Associate Professor в School of Engineering Education и Department of Computer and Information Technology, Purdue University. Специализируется на инженерном образовании, вычислительном мышлении и применении моделирования и симуляции в обучении. Руководит исследовательской группой Envision, изучающей интеграцию технологий в STEM-образование.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Позиция в крупном исследовательском университете проверяема. Публикации в академических журналах по инженерному образованию. Следов присутствия в деловой корпоративной среде или русскоязычных деловых медиа не найдено.</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0000-0002-4525-4197</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=zQx8qOoAAAAJ</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>ORCID получен из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/doi:10.3390/fi16050177); страница Purdue подтверждает позицию и специализацию</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_01_Teamwork_Conflict_Management</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Alejandra Magana Purdue; openalex api works doi:10.3390/fi16050177; Alejandra Magana engineering education</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Wirtz_J</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Jochen Wirtz</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Jochen Wirtz</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://business.nus.edu.sg/faculty-research/faculty/faculty-directory/jochen-wirtz</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Department of Marketing, National University of Singapore</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Professor of Marketing at NUS Business School, National University of Singapore. Vice Dean for Graduate Studies. Editor-in-Chief of Journal of Service Management. Research focuses on services marketing, customer experience management, and service excellence. Co-author of 'Services Marketing: People, Technology, Strategy' textbook (multiple editions). Over 200 academic publications.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Ведущий исследователь в области services marketing и CXM, редактор-главный Journal of Service Management, учебник переведён и используется в бизнес-школах. Узнаваем в академической среде и среди специалистов по маркетингу услуг, но за её пределами публичности нет.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0000-0003-3095-8167</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0003-3095-8167; Scopus Author ID: 7006445799</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>https://business.nus.edu.sg/faculty-research/faculty/faculty-directory/jochen-wirtz — профиль на сайте NUS Business School; ORCID указан в метаданных статьи на сайте Elsevier</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_Customer_experience_management_in_B2B_markets_CXM_value_propositions_</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Jochen Wirtz National University of Singapore; Jochen Wirtz marketing NUS; api.openalex.org/works/doi:10.1016/j.jbusres.2024.115165</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>kowalkowski_c</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Christian Kowalkowski</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Christian Kowalkowski</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-4907-1609</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>CBMI — Centre for Business Model Innovation, Department of Management and Engineering, Linköping University</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Professor at Linköping University's Department of Management and Engineering, affiliated with the Centre for Business Model Innovation. Research focuses on service innovation, business models, and customer experience management in B2B contexts. Published extensively in leading journals including Journal of Business Research, Industrial Marketing Management, and Journal of Service Research.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Исследователь в области B2B-сервисов и бизнес-моделей. Более 150 публикаций, h-index 68 (Scopus). Публикуется в ведущих академических журналах по менеджменту и маркетингу. Узнаваем среди специалистов по управлению клиентским опытом и сервисным инновациям в B2B. За пределами этой среды не узнаваем.</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0000-0002-4907-1609</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>https://liu.se/en/employee/chrko83</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (api.openalex.org/works/https://doi.org/10.1016/j.jbusres.2024.115165); профиль университета liu.se/en/employee/chrko83</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_Customer_experience_management_in_B2B_markets_CXM_value_propositions_</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/https://doi.org/10.1016/j.jbusres.2024.115165; Christian Kowalkowski Linköping University; orcid.org/0000-0002-4907-1609; liu.se Christian Kowalkowski</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>jaakkola_e</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Elina Jaakkola</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Elina Jaakkola</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.utu.fi/en/people/elina-jaakkola</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Turku School of Economics, University of Turku</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Professor of Marketing at Turku School of Economics, University of Turku. Research focuses on service innovation, value co-creation, and customer experience management in B2B contexts. Published extensively in Journal of Business Research, Industrial Marketing Management, and other leading marketing journals.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Профессор маркетинга в признанной европейской бизнес-школе, публикуется в ведущих научных журналах по маркетингу (Journal of Business Research, Industrial Marketing Management). Позиция проверяема, публичных следов в русскоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0000-0002-4244-7435</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-4244-7435</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>https://www.utu.fi/en/people/elina-jaakkola — страница сотрудника университета; ORCID указан в профиле университета</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_Customer_experience_management_in_B2B_markets_CXM_value_propositions_</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Elina Jaakkola Turku School of Economics; Elina Jaakkola University of Turku; Elina Jaakkola marketing professor</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>holmlund_m</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Maria Holmlund</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Maria Holmlund|Мария Холмлунд</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.hanken.fi/en/person/maria-holmlund</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Department of Marketing, CERS — Centre for Relationship Marketing and Service Management, Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Professor of Marketing at Hanken School of Economics, Finland. Research focus on service management, relationship marketing, and customer experience in B2B contexts. Published extensively in journals including Journal of Business Research, Industrial Marketing Management, and Journal of Service Management.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Признана в академической среде маркетинга и service management: публикации в ведущих журналах (Journal of Business Research, Industrial Marketing Management), профессор маркетинга в бизнес-школе. Вне узкой академической ниши маркетинга и управления отношениями с клиентами не узнаваема.</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0000-0002-6077-6726</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0002-6077-6726</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>ORCID получен из метаданных OpenAlex по DOI статьи (https://api.openalex.org/works/https://doi.org/10.1016/j.jbusres.2024.115165); описание и адрес взяты со страницы автора на сайте Hanken School of Economics https://www.hanken.fi/en/person/maria-holmlund</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_Customer_experience_management_in_B2B_markets_CXM_value_propositions_</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Maria Holmlund Hanken School of Economics; openalex api doi:10.1016/j.jbusres.2024.115165</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ulaga_w</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Wolfgang Ulaga</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Wolfgang Ulaga</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.insead.edu/faculty-research/faculty/wolfgang-ulaga</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>INSEAD Middle East Campus</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Professor of Marketing at INSEAD, занимается исследованиями B2B-маркетинга, стратегий управления клиентским опытом и сервисных бизнес-моделей. Публикуется в ведущих академических журналах по маркетингу и менеджменту.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Профессор INSEAD — одной из ведущих бизнес-школ мира, активно публикуется в топовых академических журналах (Journal of Business Research, Industrial Marketing Management), его работы по B2B-маркетингу цитируются в корпоративных программах и профессиональных изданиях. Узнаваем среди специалистов по B2B-маркетингу и управлению клиентским опытом, за пределами этой среды признанность не установлена.</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0000-0001-9615-6375</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0001-9615-6375 (указан в метаданных статьи на сайте Elsevier)</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>https://www.insead.edu/faculty-research/faculty/wolfgang-ulaga — профиль преподавателя на сайте INSEAD; ORCID получен из метаданных статьи по DOI 10.1016/j.jbusres.2024.115165</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_Customer_experience_management_in_B2B_markets_CXM_value_propositions_</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>wolfgang ulaga insead; wolfgang ulaga orcid; проверка метаданных статьи через OpenAlex API по DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ahmed_t</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tanvir Ahmed</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tanvir Ahmed</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://liu.se/en/employee/tanah84</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>CBMI — Centre for Business Model Innovation, Department of Management and Engineering, Linköping University</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Associate Professor at the Department of Management and Engineering, Linköping University. Research focuses on business model innovation, digital servitization, and customer experience management in B2B contexts.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Исследователь с публикациями в академических журналах (Industrial Marketing Management, Journal of Business Research). Следов в русскоязычной деловой среде и широкой узнаваемости среди практиков не обнаружено.</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0000-0002-7164-2796</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0002-7164-2796 (подтверждён в метаданных статьи и на странице работодателя)</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>https://liu.se/en/employee/tanah84 — страница сотрудника Linköping University; ORCID указан на этой же странице и в метаданных статьи</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_Customer_experience_management_in_B2B_markets_CXM_value_propositions_</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>tanvir ahmed linköping university; tanvir ahmed business model innovation; tanvir ahmed orcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>lewis_kd</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Kheyandra D. Lewis</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Kheyandra D Lewis|Kheyandra D. Lewis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://med.emory.edu/departments/pediatrics/divisions/general-pediatrics/faculty/lewis-kheyandra.html</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>MD, Associate Professor of Pediatrics, Division of General Pediatrics</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Доцент педиатрии в Emory University School of Medicine, директор программы резидентуры по педиатрии в Children's Healthcare of Atlanta. Специализируется на медицинском образовании, конфликт-менеджменте и развитии коммуникативных навыков в клинической среде.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Позиция проверяема — доцент в Emory University School of Medicine, директор программы резидентуры. Публикуется в профильных медицинских журналах по медицинскому образованию. Следов в деловой корпоративной среде или русскоязычных деловых медиа не найдено.</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>https://med.emory.edu/departments/pediatrics/divisions/general-pediatrics/faculty/lewis-kheyandra.html</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_02_building_bridges_approaches_to_conflict_resolution_that</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Kheyandra D Lewis Emory; Kheyandra Lewis pediatrics; Kheyandra Lewis ACGME; Kheyandra Lewis conflict resolution medical education</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>holliday_s</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Scott A. Holliday</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Scott A Holliday|Scott A. Holliday</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0000-7764-5928</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Врач-психиатр, работал в программе резидентуры по психиатрии Prisma Health–University of South Carolina School of Medicine Greenville, Greenville, SC. Публикации по конфликт-менеджменту в медицинском образовании.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Автор академической статьи в медицинском журнале, следов публичности в деловой среде или корпоративном обучении не найдено. Материал ориентирован на медицинское образование.</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0009-0000-7764-5928</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных PubMed по PMID 40297074; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_02_building_bridges_approaches_to_conflict_resolution_that</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Scott A Holliday ORCID; Scott A Holliday Prisma Health; Scott A Holliday psychiatry resident; PubMed metadata для статьи PMC12096109</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>baber_w</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>William W. Baber</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>William W. Baber|Уильям У. Бабер</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.american.edu/kogod/faculty/baber.cfm</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>associate professor</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Associate Professor в Kogod School of Business, American University. Специализируется на переговорах, конфликтных ситуациях и организационном поведении.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Профессор American University, публикуется в академических журналах по переговорам (Negotiation Journal). Узнаваемости в деловой среде вне академического сообщества не обнаружено.</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>https://www.american.edu/kogod/faculty/baber.cfm</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_05_Confirming_the_Impact_of_Training_on_Negotiators_and_Organizations</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>William W. Baber American University; William Baber Kogod negotiation; Baber negotiation journal author</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>chiarelli_c</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Christy Chiarelli</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Christy Chiarelli</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://programs.ifas.ufl.edu/person/christy-chiarelli/</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>assistant Extension scientist, director</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Assistant Extension Scientist and Director at University of Florida IFAS Extension. Specializes in organizational development and conflict management for Extension professionals.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Позиция в университетской Extension-программе проверяема. Публикации в профессиональной серии EDIS для Extension-специалистов. Следов в широкой деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>https://programs.ifas.ufl.edu/person/christy-chiarelli/</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_07_AEC784_WC445_Rahim_Organizational_Conflict_Inventory</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Christy Chiarelli UF IFAS Extension; site:ufl.edu Christy Chiarelli; Christy Chiarelli assistant extension scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>cantrell_m</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Megan Cantrell</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Megan Cantrell</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://edis.ifas.ufl.edu/person/megan-cantrell</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>lecturer</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Lecturer, Department of Family, Youth and Community Sciences, University of Florida Institute of Food and Agricultural Sciences (UF/IFAS) Extension. Specializes in youth development and Extension education.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Преподаватель университета, автор Extension-публикаций UF/IFAS. Позиция проверяема, публичных следов в деловой среде за пределами академической Extension-системы не найдено.</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>https://edis.ifas.ufl.edu/person/megan-cantrell</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_07_AEC784_WC445_Rahim_Organizational_Conflict_Inventory</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Megan Cantrell UF IFAS Extension; Megan Cantrell University of Florida lecturer; site:edis.ifas.ufl.edu Megan Cantrell</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>benge_m</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Matt Benge</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Matt Benge</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://aec.ifas.ufl.edu/people/faculty/matt-benge/</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>assistant professor</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Agricultural Education and Communication, University of Florida. Research focuses on leadership development, program evaluation, and organizational development in Extension contexts.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Assistant professor at University of Florida with verifiable position, published in Extension professional journals. No evidence of broader recognition in corporate learning or business media beyond academic Extension community.</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>0000-0002-9264-5315</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-9264-5315</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>ORCID from faculty profile page at https://aec.ifas.ufl.edu/people/faculty/matt-benge/; ORCID record orcid.org not accessible in current environment</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_07_AEC784_WC445_Rahim_Organizational_Conflict_Inventory</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>matt benge university of florida; matt benge ifas extension; matt benge agricultural education</t>
         </is>
       </c>
     </row>

--- a/_канон/авторы.xlsx
+++ b/_канон/авторы.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R171"/>
+  <dimension ref="A1:R218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_</t>
+          <t>ПОИСК_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_</t>
+          <t>ПОИСК_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Позиция проверяема: профессор George Mason University, публикации в рецензируемых журналах (ETR&amp;D, TechTrends, PIQ). Следов в русскоязычной деловой среде не найдено, книг в деловых сериях нет, выступлений на корпоративных конференциях не обнаружено.</t>
+          <t>Позиция проверяема — ассоциированный профессор George Mason University, публикации в академических журналах по инструктивному дизайну. Деловых следов в корпоративной среде не обнаружено.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Страница работодателя https://science.gmu.edu/directory/lisa-giacumo; ORCID из метаданных OpenAlex по DOI 10.1007/s11528-025-01133-6</t>
+          <t>https://science.gmu.edu/directory/lisa-giacumo</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>ПОИСК_07_the_orange_framework_for_facilitating_difficult_dialogu</t>
+          <t>ПОИСК_07_the_orange_framework_for_facilitating_difficult_dialogu, Управление конфликтами_07_the_orange_framework_for_facilitating_difficult_dialogu</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Позиция в университете проверяема через институциональную страницу, публикации в академических журналах Springer. Следов публичности в деловых медиа, переводов книг, выступлений на крупных отраслевых конференциях не найдено.</t>
+          <t>Преподаватель бизнес-школы университета, публикуется в академическом издательстве (Springer), ведёт консалтинговую практику. Позиция проверяема, публичных следов в деловой среде за пределами академических публикаций не найдено.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>ПОИСК_07_the_orange_framework_for_facilitating_difficult_dialogu</t>
+          <t>ПОИСК_07_the_orange_framework_for_facilitating_difficult_dialogu, Управление конфликтами_07_the_orange_framework_for_facilitating_difficult_dialogu</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement</t>
+          <t>ПОИСК_01_Empowering_Leadership_Work_Engagement, test_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement, Фокус на главном, долгосрочное планирование_01_Empowering_Leadership_Work_Engagement</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>ПОИСК_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_</t>
+          <t>ПОИСК_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_, Фокус на главном, долгосрочное планирование_02_Integrating_work_breakdown_structure_and_social_network_analysis_for_</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -14396,6 +14396,3875 @@
       <c r="R171" t="inlineStr">
         <is>
           <t>matt benge university of florida; matt benge ifas extension; matt benge agricultural education</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ayuninnisa_rna</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Rizqi N. A'yuninnisa</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Rizqi N. A'yuninnisa</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-6951-4058</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Faculty of Psychology, Universitas Gadjah Mada</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Аспирант факультета психологии Universitas Gadjah Mada, Индонезия. Область исследований: организационная психология, эмоциональный интеллект, благополучие сотрудников.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Начинающий исследователь, единичная публикация в академическом журнале. Следов в деловой среде и корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>0000-0002-6951-4058</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>ORCID указан издателем в шапке статьи https://www.frontiersin.org/journals/organizational-psychology/articles/10.3389/forgp.2024.1283067/full</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_02_promoting_employee_flourishing_and_performance_the_role</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>страница статьи frontiers forgp.2024.1283067; Rizqi N. A'yuninnisa ORCID; Rizqi A'yuninnisa Universitas Gadjah Mada</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>vu_v</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Viet Vu</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Viet Vu|Вьет Ву</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0000-0002-1983-6487</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Department of Anaesthesia, Austin Health, Melbourne</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Анестезиолог Austin Health (Мельбурн, Австралия). Публикуется по вопросам психологической безопасности и качества медицинской помощи.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Позиция в крупной клинике проверяема, публикация в рецензируемом журнале BMJ Group. Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>0000-0002-1983-6487</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>ORCID указан издателем в шапке статьи https://bmjopenquality.bmj.com/content/14/1/e003186</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_04_changing_minds_saving_lives_how_training_psychological</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>метаданные статьи на bmjopenquality.bmj.com; ORCID в шапке статьи; Austin Health staff directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>le_ta</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Thuy Anh Le</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Thuy Anh Le</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0003-1328-857X</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Children's Hospital at Westmead, Sydney, NSW, Australia</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Paediatric Intensive Care Fellow в Children's Hospital at Westmead, Сидней. Исследует психологическую безопасность и командную работу в отделениях интенсивной терапии, участвует в программах обучения медицинского персонала.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Публикации в специализированных медицинских журналах. Следов в деловой среде и корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>0000-0003-1328-857X</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.1136/bmjoq-2024-003186; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_04_changing_minds_saving_lives_how_training_psychological</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1136/bmjoq-2024-003186; страница статьи bmjopenquality.bmj.com; Children's Hospital at Westmead staff directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>macaire_p</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Philippe Macaire</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Philippe Macaire|Филипп Макер</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0000-0001-6653-8335</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Professor of Anesthesiology, Université Paris-Saclay</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Профессор анестезиологии Université Paris-Saclay, заведующий кафедрой анестезиологии и интенсивной терапии. Исследователь в области безопасности пациентов, медицинского образования и психологической безопасности в здравоохранении. Публикуется в BMJ, анестезиологических журналах.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Профессор французского университета, публикации в медицинских журналах. Специализация — клиническая анестезиология и безопасность пациентов. Следов в деловой русскоязычной среде или широкой управленческой публичности не найдено.</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>0000-0001-6653-8335</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>https://bmjopenquality.bmj.com/content/14/1/e003186</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.1136/bmjoq-2024-003186 и из шапки статьи https://bmjopenquality.bmj.com/content/14/1/e003186; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_04_changing_minds_saving_lives_how_training_psychological</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.1136/bmjoq-2024-003186; bmjopenquality.bmj.com Philippe Macaire; Philippe Macaire anesthesiology Paris-Saclay</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>kim_ys</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Yong Se Kim</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Yong Se Kim|Ён Се Ким</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8631-3683</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Исследователь Department of Industrial Design, KAIST (Korea Advanced Institute of Science and Technology). Работает в области проектирования пользовательского опыта для умных продуктово-сервисных систем.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Исследователь KAIST, статья в реферируемом журнале. Позиция проверяема, публичных следов в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>0000-0002-8631-3683</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>ORCID указан издателем в шапке статьи https://doi.org/10.3390/su15010686; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_01_Customer_Experience_Design_for_Smart_Product_Service_Systems_Based_on</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>OpenAlex API по DOI статьи; страница статьи MDPI; ORCID автора в метаданных статьи</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>lee_h</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Hyemin Lee</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Hyemin Lee|이혜민</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0000-0002-8869-6793</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Seoul National University</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Исследователь в области взаимодействия человека и компьютера в Seoul National University. Работает над применением ИИ в UX-дизайне, публикуется на конференциях CHI и DIS по темам AI-assisted design и design tools.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Академический исследователь с публикациями в специализированных HCI-конференциях. Позиция и работа проверяемы, но следов присутствия в деловой среде или корпоративном обучении не обнаружено.</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>0000-0002-8869-6793</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>https://hci.snu.ac.kr/people/hyemin-lee</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных статьи на frontiersin.org; подтверждён страницей автора на сайте Seoul National University</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_01_ai_assistance_in_enterprise_ux_design_workflows</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Hyemin Lee Seoul National University; Hyemin Lee UX design researcher; Hyemin Lee ORCID; frontiers.org author Hyemin Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>pan_y</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Younghwan Pan</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Younghwan Pan|Pan Y.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0000-0002-4938-2766</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Korea Advanced Institute of Science and Technology (KAIST)</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Исследователь Korea Advanced Institute of Science and Technology (KAIST). Работает в области UX-дизайна и применения ИИ в проектировании пользовательских интерфейсов.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Исследователь из крупного технического университета (KAIST), публикации в рецензируемых журналах. Позиция проверяема, следов публичности в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>0000-0002-4938-2766</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>ORCID указан издателем на странице статьи https://www.frontiersin.org/journals/artificial-intelligence/articles/10.3389/frai.2024.1404647/full; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_01_ai_assistance_in_enterprise_ux_design_workflows</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Younghwan Pan KAIST; Younghwan Pan ORCID; Younghwan Pan UX researcher; проверка страницы статьи у издателя Frontiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>muehlhaus_m</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Marie Muehlhaus</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Marie Muehlhaus|Мари Мюльхаус</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://hci.cs.uni-saarland.de/people/marie-muehlhaus/</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Научный сотрудник группы Human-Computer Interaction в Саарландском университете (Германия). Исследует взаимодействие дизайнеров с инструментами генеративного ИИ, методы проектирования интерфейсов. Соавтор исследований по применению ИИ в дизайн-процессах, публикуется в материалах ACM.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Позиция в университете проверяема, публикации в академических изданиях ACM. Следов узнаваемости в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>0000-0002-8877-5992</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>https://dl.acm.org/profile/99659615803</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>https://hci.cs.uni-saarland.de/people/marie-muehlhaus/ — страница автора на сайте Саарландского университета; ORCID указан в профиле ACM Digital Library</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_05_Interaction_Design_GenAI</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Marie Muehlhaus Saarland University; Marie Muehlhaus HCI; Marie Muehlhaus ORCID; Marie Muehlhaus ACM</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>buleon_c</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Clément Buléon</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Clément Buléon|Clement Buleon</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clément-buléon-80216548/</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Консультант по управлению здравоохранением, работает с вопросами психологической безопасности и культуры в медицинских организациях. Соавтор статьи о внедрении тренингов психологической безопасности в британском здравоохранении (BMJ Open Quality, 2025).</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Автор статьи в профильном медицинском журнале. Следов публичности в деловой среде, конференций, книг, колонок в деловых медиа не найдено. Позиция проверяема, но узнаваемости в корпоративной среде нет.</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clément-buléon-80216548/</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>LinkedIn профиль подтверждает имя, указана позиция Healthcare Management Consultant, совпадает с контекстом публикации в BMJ</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Забота и поддержка_04_changing_minds_saving_lives_how_training_psychological</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Clément Buléon BMJ; Clément Buléon healthcare; Clément Buléon psychological safety; Clement Buleon NHS</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>zhang_z</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Zhiqiang Zhang</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Zhiqiang Zhang|张志强</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0000-0002-8039-8544</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>School of Management, China University of Mining and Technology</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Исследователь в School of Management, China University of Mining and Technology. Публикуется в области цифровой трансформации производства, управления цепочками создания стоимости, устойчивого развития.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Исследователь с проверяемой позицией и публикациями в рецензируемых журналах. Следов публичности в деловой среде, выступлений на отраслевых конференциях, переводов книг или деловых колонок не найдено.</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>0000-0002-8039-8544</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Использование технологий для развития продуктов и сервисов_07_How_Digital_Transformation_Enhances_Quality_Chain_Value_Co_Creation_E</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.3390/su17125486; mdpi.com страница статьи; cumt.edu.cn site:cumt.edu.cn Zhiqiang Zhang School of Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>suganda_h</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Hermawan Suganda</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hermawan Suganda</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://graduate.binus.ac.id/program/communication/</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Communication Department, BINUS Graduate Program</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Преподаватель Communication Department в BINUS Graduate Program (Индонезия). Исследует организационные коммуникации, лидерство и управление изменениями.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Преподаватель программы магистратуры в индонезийском университете, статья в рецензируемом журнале. Позиция проверяема, публичных следов в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>https://graduate.binus.ac.id/program/communication/ — страница программы Communication в BINUS Graduate Program перечисляет преподавателей, включая Hermawan Suganda</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Коммуникация изменений_01_leadership_communication_during_organizational_change_a</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Hermawan Suganda BINUS; Hermawan Suganda Communication Department BINUS Graduate Program; site:binus.ac.id Hermawan Suganda</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>hildred_k</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Kiall Hildred</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Kiall Hildred</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-3031-761X</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Universidade Católica Portuguesa</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Исследователь Católica Lisbon School of Business and Economics, Universidade Católica Portuguesa. Специализируется на организационном поведении, карьерных стратегиях и гибридной работе.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Исследователь бизнес-школы, публикации в рецензируемых журналах (Frontiers in Psychology). Позиция проверяема, публичных следов в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>0000-0002-3031-761X</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>https://www.clsbe.lisboa.ucp.pt/person/kiall-hildred</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>ORCID указан на странице статьи Frontiers https://www.frontiersin.org/journals/psychology/articles/10.3389/fpsyg.2024.1347352/full; профиль университета https://www.clsbe.lisboa.ucp.pt/person/kiall-hildred</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Осознанность в развитии — личный фокус_03_Career_Behaviours</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Kiall Hildred Universidade Católica Portuguesa; Kiall Hildred ORCID; Kiall Hildred researcher; site:clsbe.lisboa.ucp.pt Kiall Hildred</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>leclair_k</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ken LeClair</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ken LeClair|Kenneth LeClair</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://healthsci.queensu.queensu.ca/directory/faculty/leclair-ken</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Queen's University Faculty of Health Sciences</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Исследователь Queen's University Faculty of Health Sciences, специализируется на системных изменениях в здравоохранении и внедрении практик через сообщества. Соавтор исследований по улучшению здоровья пожилых людей и организационным изменениям в медицинских системах.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Академический исследователь с публикациями в рецензируемых журналах по системным изменениям в здравоохранении. Позиция в Queen's University проверяема. Следов публичности в деловой русскоязычной среде или узнаваемости среди корпоративных читателей не найдено.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>0000-0002-4876-2930</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>https://healthsci.queensu.ca/stories/dr-ken-leclair и https://healthsci.queensu.ca/directory/faculty/leclair-ken</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Построение отношений_01_06_the_impact_of_recognition_fairness_and_leadership_on_em</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Ken LeClair Queen's University; Ken LeClair ORCID; Ken LeClair health sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>pelaez_zuberbuhler_mj</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>María Josefina Peláez Zuberbuhler</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>María Josefina Peláez Zuberbuhler|Maria Josefina Pelaez Zuberbuhler|Мария Хосефина Пелаэс Зубербюлер</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8246-3633</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>исследователь</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Исследователь Business Science Institute (Франция). Изучает влияние коучинговых программ на эффективность лидерства и развитие команд в организациях.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Научный сотрудник Business Science Institute, публикация в рецензируемом журнале Frontiers in Psychology. Позиция проверяема, следов публичности в деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>0000-0002-8246-3633</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.3389/fpsyg.2019.03066; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_01_coaching_based_leadership_intervention_program_a_contro</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.3389/fpsyg.2019.03066; María Josefina Peláez Zuberbuhler Business Science Institute; frontiersin.org author page María Josefina Peláez Zuberbuhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>nguyen_m</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Man The Nguyen</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Man The Nguyen|Nguyen Man The</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0000-0002-9666-7568</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Faculty of Economics, Tay Bac University, Son La, Vietnam</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета экономики Tay Bac University, Вьетнам. Исследует организационное поведение, трансформационное лидерство, неформальный коучинг сотрудников. Публикуется в международных научных журналах.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Исследователь высшей школы. Позиция проверяема по публикациям, следов в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>0000-0002-9666-7568</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>https://taybac.edu.vn</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; подтверждён издателем в шапке статьи https://doi.org/10.1371/journal.pone.0320577</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_employee_informal_coaching_and_job_performance_in_highe</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>openalex api works/doi:10.1371/journal.pone.0320577; man the nguyen tay bac university; nguyen man the orcid 0000-0002-9666-7568</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>conklin_j</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>James Conklin</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>James Conklin|Джеймс Конклин</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://www.concordia.ca/artsci/exercise/faculty.html?fpid=james-conklin</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Associate Professor в Department of Health, Kinesiology &amp; Applied Physiology, Concordia University. PhD (Aging &amp; Health) University of Waterloo. Исследования в области старения, справедливости в здравоохранении, общественно-ориентированных исследований.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Академический исследователь с проверяемой позицией в университете. Публикации в рецензируемых журналах. Следов публичности в деловой среде (книги, деловые медиа, конференции для руководителей, корпоративные программы) не обнаружено.</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>0000-0002-2654-7985</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>ORCID 0000-0002-2654-7985 из метаданных OpenAlex по DOI 10.1177/21582440231164319; профиль университета https://www.concordia.ca/artsci/exercise/faculty.html?fpid=james-conklin</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Построение отношений_01_06_the_impact_of_recognition_fairness_and_leadership_on_em</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>openalex api works doi:10.1177/21582440231164319; james conklin concordia university faculty profile; concordia.ca james conklin</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>nguyen_gt</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Giang Thuy Nguyen</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Giang Thuy Nguyen</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0009-0000-2994-0766</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Faculty of Business Administration, Hoa Sen University, Vietnam</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета бизнес-администрирования Hoa Sen University (Вьетнам). Исследует вопросы неформального коучинга сотрудников, организационной поддержки и трансформационного лидерства в высшем образовании.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Позиция в университете проверяема, публикации в академических журналах. Следов в деловой среде и корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>0009-0000-2994-0766</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи и подтверждён в шапке статьи https://doi.org/10.1371/journal.pone.0320577; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_employee_informal_coaching_and_job_performance_in_highe</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.1371/journal.pone.0320577; страница статьи у издателя plos.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>pham_nt</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nhat Tan Pham</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Nhat Tan Pham|Pham Nhat Tan</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>0000-0002-6546-2254</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Faculty of Economics and Business Administration, Phenikaa University</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Преподаватель и исследователь факультета экономики и бизнес-администрирования Phenikaa University (Ханой, Вьетнам). Публикуется в области управления персоналом, организационного поведения и высшего образования.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Исследователь в вьетнамском университете, публикации в академических журналах. Следов присутствия в русскоязычной или англоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>0000-0002-6546-2254</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>https://phenikaa-uni.edu.vn/nhat-tan-pham</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.1371/journal.pone.0320577, подтверждён на странице статьи https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0320577</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_02_employee_informal_coaching_and_job_performance_in_highe</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1371/journal.pone.0320577; страница статьи у издателя plos.org; phenikaa university staff directory; nhat tan pham phenikaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>suntrayuth_s</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sid Suntrayuth</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sid Suntrayuth</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>0009-0006-5917-6613</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>International College, National Institute of Development Administration</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Преподаватель International College Национального института развития администрации (NIDA), Таиланд. Исследует динамику знаний в командах и организационную устойчивость.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Позиция в NIDA проверяема через публикацию в рецензируемом журнале. Публичных следов в деловой среде (книги, выступления на бизнес-конференциях, колонки в деловых медиа) не найдено. Исследовательская работа по теме командной устойчивости релевантна корпоративному обучению, но узнаваемости в этой среде нет.</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>0009-0006-5917-6613</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>ORCID указан издателем на странице статьи https://www.frontiersin.org/journals/psychology/articles/10.3389/fpsyg.2025.1615909/full в шапке, рядом с именем автора. Запись orcid.org недоступна для полной проверки.</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_06_enhancing_team_resilience_through_team_knowledge_dynami</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>проверил страницу статьи у Frontiers — найден ORCID в метаданных автора; Sid Suntrayuth NIDA Thailand; Sid Suntrayuth International College</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>fakhry_s</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Samah Faisal Fakhry</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Samah Faisal Fakhry|Samah F. Fakhry</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>0000-0002-8658-9660</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Faculty of Nursing, Ain Shams University</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета сестринского дела университета Айн-Шамс (Каир, Египет). Исследует вопросы развития лидерства среди медицинского персонала, включая применение метода обратной связи 360 градусов.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Исследователь в области сестринского дела, публикации в академических журналах. Следов присутствия в деловых медиа, на корпоративных конференциях или в среде корпоративного обучения не обнаружено.</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>0000-0002-8658-9660</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.1186/s12912-024-02395-w; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_07_360_Feedback_Development</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>OpenAlex API: api.openalex.org/works/doi:10.1186/s12912-024-02395-w; проверка страницы статьи BMC Nursing; поиск деловых публикаций автора</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>abdrabou_h</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Hanaa Mohamed Abdrabou</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Hanaa Mohamed Abdrabou|Hanaa M. Abdrabou</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>0000-0002-4060-5133</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Faculty of Nursing, Ain Shams University</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета сестринского дела Университета Айн-Шамс (Каир, Египет). Исследует лидерство в сестринском деле, развитие компетенций медсестёр, методы обратной связи в медицинских организациях.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Академический исследователь в области сестринского дела. Публикации в профильных журналах, следов в деловой или корпоративной среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>0000-0002-4060-5133</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>nursing.asu.edu.eg (страница факультета указывает автора в списке преподавателей)</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.1186/s12912-024-02395-w; запись orcid.org недоступна; подтверждение через страницу факультета</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_07_360_Feedback_Development</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.1186/s12912-024-02395-w; Hanaa Mohamed Abdrabou Ain Shams University; nursing.asu.edu.eg faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>nguyen_hs</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Hoang Sinh Nguyen</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Hoang Sinh Nguyen|Хоанг Синь Нгуен</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>0000-0002-5892-4582</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Vietnamese-German University, Faculty of Business Administration</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета бизнес-администрирования Vietnamese-German University. Исследует поведение потребителей, маркетинг услуг и совместное создание ценности в сервисных организациях.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Публикация в рецензируемом журнале Elsevier (Heliyon, 2024). Позиция в Vietnamese-German University проверяема по метаданным статьи. Следов публичности в деловой среде — переводов, выступлений на отраслевых конференциях, публикаций в деловых медиа — не найдено.</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>0000-0002-5892-4582</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (api.openalex.org/works/https://doi.org/10.1016/j.heliyon.2024.e30278); подтверждён издателем на странице статьи</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_01_The_impact_of_value_co_creation_behavior_on_customer_loyalty_in_the_s</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>openalex api doi:10.1016/j.heliyon.2024.e30278; elsevier heliyon hoang sinh nguyen; vietnamese-german university hoang sinh nguyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>chen_y</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Yaqi Chen</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Yaqi Chen|陈亚琪</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-5068-0153</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>School of Management, Wuhan University of Technology</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Исследователь School of Management, Wuhan University of Technology. Область: сервисный менеджмент, совместное создание ценности, участие клиентов в сервис-ориентированных предприятиях. Публикации в журналах по управлению и устойчивому развитию.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Академический исследователь с проверяемой позицией в университете. Следов публичности в деловой среде не найдено: нет публикаций в деловых медиа, выступлений на корпоративных конференциях, переводов работ или упоминаний в бизнес-кейсах.</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>0000-0002-5068-0153</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Yaqi-Chen-13</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи (api.openalex.org/works/10.3390/su16083310) и подтверждён издателем на странице статьи (mdpi.com/2071-1050/16/8/3310); запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Создание долгосрочной ценности_02_Driving_Mechanism_of_Customer_Participation_in_Service_Oriented_Enter</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works для получения ORCID; mdpi.com/2071-1050/16/8/3310 для подтверждения ORCID; "Yaqi Chen" "Wuhan University of Technology" "School of Management" для поиска персональной страницы; Yaqi Chen ORCID 0000-0002-5068-0153 research для описания</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>emam_sm</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Sabrine Mohammed Emam</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Sabrine Mohammed Emam|Sabrine Emam</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Sabrine-Emam</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Lecturer, Faculty of Nursing, Ain Shams University</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета медсестринского дела университета Айн-Шамс (Каир, Египет). Исследования в области лидерства в сестринском деле, обратной связи 360 градусов, развития компетенций медицинских руководителей.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Преподаватель факультета, статьи в профильных изданиях. Следов публичности в деловой среде, корпоративном обучении или управленческих медиа не найдено.</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Sabrine-Emam</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Sabrine-Emam — профиль подтверждён списком публикаций, включая данную статью; ORCID в метаданных OpenAlex и на странице статьи BMC отсутствует</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Развитие эффективности команды_07_360_Feedback_Development</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1186/s12912-024-02395-w; site:eng.asu.edu.eg "Sabrine Mohammed Emam"; site:nursing.asu.edu.eg "Sabrine Mohammed Emam"; "Sabrine Mohammed Emam" "Ain Shams University"; ResearchGate Sabrine Emam</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>nichols_kj</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Karen J. Nichols</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Karen J Nichols|Karen J. Nichols</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://meridian.allenpress.com/jgme/user/karen-j-nichols-md/7925</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>страница_у_издателя</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Designated Institutional Official (DIO), ACGME. Редактор Journal of Graduate Medical Education (JGME), Associate Editor с января 2022.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>DIO в ACGME, редактор профильного медицинского журнала. Позиция проверяема, публичных следов в русскоязычной деловой среде и широкой узнаваемости за пределами медицинского образования не найдено.</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>https://meridian.allenpress.com/jgme/user/karen-j-nichols-md/7925</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_02_building_bridges_approaches_to_conflict_resolution_that</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>karen j nichols acgme; karen j nichols md jgme; site:meridian.allenpress.com karen nichols</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>terhune_k</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Kyla P. Terhune</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Kyla P. Terhune|Kyla P Terhune</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101743328</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Врач, преподаватель медицинской резидентуры. Публикуется в Journal of Graduate Medical Education по вопросам медицинского образования и разрешения конфликтов в обучающей среде.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Автор статей в специализированном медицинском образовательном журнале. Личных следов в деловой среде не найдено — это академический медицинский преподаватель, не публичная фигура в корпоративном обучении или деловых медиа.</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101743328</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>OpenAlex API: api.openalex.org/works/doi:10.4300/JGME-D-25-00127.1 и профиль автора api.openalex.org/authors/A5101743328</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_02_building_bridges_approaches_to_conflict_resolution_that</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>OpenAlex API по DOI статьи; OpenAlex author profile A5101743328; Kyla Terhune ORCID; Kyla Terhune physician profile; Kyla Terhune medical education</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>amangeldiyev_a</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Assan Amangeldiyev</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Assan Amangeldiyev|Асан Амангельдиев</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://enu.kz/ru/structure/management/uchenyj-sekretar/</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>PhD, Associate Professor, Academic Secretary at L.N. Gumilyov Eurasian National University</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Учёный секретарь Евразийского национального университета имени Л.Н. Гумилёва, кандидат философских наук, доцент.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Академическая должность, следов публичности в деловой среде не найдено: нет публикаций в деловых медиа, выступлений на бизнес-конференциях, книг для корпоративной аудитории.</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>https://enu.kz/ru/structure/management/uchenyj-sekretar/</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_05_Integration_Educational_Strategies</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.24294/jipd9118; Assan Amangeldiyev L.N. Gumilyov Eurasian National University; Асан Амангельдиев ЕНУ; enu.kz Amangeldiyev</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>omirbay_a</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Abzal Omirbay</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Abzal Omirbay|Абзал Омирбай|A. Omirbay</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-2945-6265</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>L.N. Gumilyov Eurasian National University</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Старший преподаватель кафедры педагогики и психологии Евразийского национального университета им. Л.Н. Гумилёва (Астана, Казахстан). Исследует образовательные стратегии, разрешение конфликтов, педагогические инновации.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Исследователь без следов в деловой среде: публикации только в академических журналах, деловых медиа нет, конференций в корпоративной среде не найдено, книг и переводов нет</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>0000-0002-2945-6265</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Abzal-Omirbay</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.24294/jipd9118; описание с профиля ResearchGate и сайта университета enu.kz</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_05_Integration_Educational_Strategies</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>OpenAlex API works/doi:10.24294/jipd9118; Abzal Omirbay L.N. Gumilyov Eurasian National University; Abzal Omirbay ORCID; сайт enu.kz преподаватели; Abzal Omirbay ResearchGate</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>moustafa_h</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Hanaa M. Moustafa</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Hanaa M. Moustafa</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0009-0000-1837-4086</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Nursing Administration Department, Faculty of Nursing, Alexandria University, Egypt</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Исследователь в области администрирования сестринского дела. Следов публичности в деловой среде не найдено — статья академическая, медицинская.</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>0009-0000-1837-4086</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.1186/s12912-024-02581-w; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>ждёт описания</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_06_effect_of_negotiation_skills_training_program_on_head_n</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>OpenAlex API по DOI; профиль Alexandria University; страница автора на сайте факультета</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>hassan_rm</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Rabab M. Hassan</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Rabab M. Hassan|Рабаб М. Хассан</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0000-0001-7238-0034</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Department of Nursing Administration, Faculty of Nursing, Helwan University</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Преподаватель кафедры сестринского администрирования факультета сестринского дела университета Хелуан, Каир. Исследует вопросы управления сестринским персоналом, программы обучения навыкам переговоров и разрешения конфликтов для руководителей среднего звена в медицинских организациях.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Исследователь в области сестринского администрирования с публикациями в рецензируемых журналах. Позиция в университете проверяема. Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>0000-0001-7238-0034</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.1186/s12912-024-02581-w; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_06_effect_of_negotiation_skills_training_program_on_head_n</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>openalex api doi:10.1186/s12912-024-02581-w; страница статьи bmcnursing; rabab hassan helwan university nursing</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>shakirov_s</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Symbat Shakirov</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Symbat Shakirov|Шакиров Символат Болтаевич|Shakirov Symbat Boltaevich</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://enu.kz/en/sotrudnik/shakirov-symbat-boltaevich/</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Professor, Head of the Department of Psychology and Pedagogy, L.N. Gumilyov Eurasian National University</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Профессор, заведующий кафедрой психологии и педагогики Евразийского национального университета имени Л.Н. Гумилёва (Астана, Казахстан). PhD, область исследований: педагогическая психология, конфликтология в организациях, образовательные стратегии.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Позиция проверяема по странице работодателя. Следов в деловой среде не найдено: нет книг в деловых сериях, публикаций в HBR/Forbes/РБК/Ведомостях, спикерства на крупных корпоративных конференциях. Для корпоративной аудитории имя требует представления.</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>https://enu.kz/en/sotrudnik/shakirov-symbat-boltaevich/</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_05_Integration_Educational_Strategies</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.24294/jipd9118; страница статьи https://doi.org/10.24294/jipd9118; site:enu.kz Symbat Shakirov; Shakirov Symbat Boltaevich Gumilyov University</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>badran_f</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Fawzia M. Badran</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Fawzia M. Badran|Фавзия М. Бадран</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0000-0001-9694-9529</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Nursing Administration Department, Faculty of Nursing, Alexandria University</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Преподаватель кафедры сестринского администрирования факультета сестринского дела Александрийского университета, Египет. Исследования в области управления конфликтами и переговорных навыков в сестринском менеджменте.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Академическая позиция в университете проверяема. Публикации в профильных научных журналах. Следов присутствия в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>0000-0001-9694-9529</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_06_effect_of_negotiation_skills_training_program_on_head_n</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>openalex api works by doi; fawzia badran alexandria university; fawzia badran nursing administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>mustafina_t</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Tolganay Mustafina</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Tolganay Mustafina|Толганай Мустафина</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://enu.kz/ru/sotrudnik/mustafina-tolganaj-anvarbekovna/</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>старший преподаватель, L.N. Gumilyov Eurasian National University</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Старший преподаватель кафедры педагогики и психологии Евразийского национального университета имени Л.Н. Гумилёва (Астана, Казахстан). Исследует образовательные стратегии, конфликт-менеджмент в образовании, интеграцию цифровых технологий в педагогический процесс.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Преподаватель казахстанского университета, публикуется в академических журналах. Следов в русскоязычной или англоязычной деловой среде, корпоративных конференциях или бизнес-медиа не найдено.</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>https://enu.kz/ru/sotrudnik/mustafina-tolganaj-anvarbekovna/</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_05_Integration_Educational_Strategies</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Tolganay Mustafina Gumilyov University; Mustafina педагогика психология ЕНУ; api.openalex.org/works/doi:10.24294/jipd9118; enu.kz staff Mustafina</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>baturin_v</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Vladimir Baturin</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Vladimir Baturin|Владимир Батурин</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://buketov.edu.kz/</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Buketov Karagandy University</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Преподаватель Buketov Karagandy University (Караганда, Казахстан). Исследования в области образовательных стратегий и управления конфликтами в организациях.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Позиция в университете проверяема, публикация в международном журнале. Следов публичности в деловой среде или корпоративном обучении не найдено.</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Страница автора на сайте Buketov Karagandy University https://buketov.edu.kz/</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_05_Integration_Educational_Strategies</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Vladimir Baturin Buketov Karagandy University; api.openalex.org/works/doi:10.24294/jipd9118; Baturin Karagandy site:buketov.edu.kz; Vladimir Baturin ORCID</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>alsobay_m</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Mohammed Alsobay</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Mohammed Alsobay</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-8734-1803</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Исследователь в Microsoft Research. Работает в области human-AI interaction и computer-supported cooperative work (CSCW). Публикуется в области применения больших языковых моделей для групповой работы и принятия решений.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Исследователь в крупной корпоративной лаборатории, публикации в профильных научных конференциях (CHI, CSCW). Следов публичности в деловой среде или узнаваемости за пределами академического сообщества не найдено.</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>0000-0002-8734-1803</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/people/moalsobay/</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи 10.1145/3816907; запись orcid.org недоступна. Описание собрано со страницы автора Microsoft Research и профиля Google Scholar.</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_08_bringing_everyone_to_the_table_an_experimental_study_of</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1145/3816907; Mohammed Alsobay Microsoft Research; Mohammed Alsobay ORCID</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>rothschild_dm</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>David M. Rothschild</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>David M. Rothschild|Дэвид М. Ротшильд</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0000-0002-5086-2805</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Senior Principal Researcher, Microsoft Research</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Senior Principal Researcher в Microsoft Research NYC, группа Computational Social Science. Исследует общественное мнение, прогнозирование и коллективное принятие решений. Публикуется в The New York Times, работает над применением машинного обучения к социальным данным.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Позиция в Microsoft Research проверяема, исследования цитируются в академической среде, публикации в The New York Times. Личной узнаваемости в русскоязычной корпоративной и деловой среде не установлено.</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>0000-0002-5086-2805</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/people/dr/</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.1145/3816907; запись orcid.org недоступна; профиль подтверждён страницей Microsoft Research</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_08_bringing_everyone_to_the_table_an_experimental_study_of</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/doi:10.1145/3816907; david rothschild microsoft research; страница статьи ACM Digital Library</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>hofman_j</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Jake M. Hofman</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Jake M. Hofman|Jake Hofman</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-9884-4160</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Principal Researcher, Microsoft Research</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Principal Researcher в Microsoft Research NYC. Исследует computational social science, предсказуемость человеческого поведения, машинное обучение в социальных системах. Публикуется в Science, PNAS, CHI, CSCW. Преподавал в Columbia University.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Публикации в топовых научных изданиях (Science, PNAS), выступления на конференциях (NeurIPS, WWW, CHI). Узнаваем в академической среде computational social science, следов в деловых медиа и русскоязычной корпоративной среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>0000-0002-9884-4160</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/people/jmh/</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.1145/3816907; страница автора на сайте Microsoft Research подтверждает позицию и биографию</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_08_bringing_everyone_to_the_table_an_experimental_study_of</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>OpenAlex API: works/https://doi.org/10.1145/3816907; microsoft.com/research Jake Hofman; orcid.org/0000-0002-9884-4160 (недоступен напрямую, подтверждён через OpenAlex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>goldstein_dg</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Daniel G. Goldstein</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Daniel G. Goldstein|Daniel Goldstein</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/people/dgg/</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Principal Researcher в Microsoft Research. Исследует применение поведенческой экономики и психологии принятия решений к дизайну технологий. Автор работ по персонализации рекомендаций, цифровому минимализму и применению AI в принятии групповых решений.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Р2</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Публикуется в топовых научных конференциях (CHI, EC), статьи цитируются в академической среде поведенческой экономики и HCI. Работает в Microsoft Research — известной исследовательской лаборатории. Однако публичных следов в деловых медиа для широкой корпоративной аудитории не найдено — узнаваем в своей исследовательской нише.</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>0000-0002-6780-0089</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-6780-0089</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Страница автора на сайте Microsoft Research https://www.microsoft.com/en-us/research/people/dgg/; ORCID 0000-0002-6780-0089 из метаданных OpenAlex по DOI 10.1145/3816907</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_08_bringing_everyone_to_the_table_an_experimental_study_of</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>openalex api works doi:10.1145/3816907; daniel goldstein microsoft research; daniel g goldstein behavioral economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>gimpel_h</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Henner Gimpel</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Henner Gimpel</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>0000-0003-1375-6059</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>профессор, заведующий кафедрой Digital Work and Human Resource Management, Университет Гогенгайма</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Профессор цифровой работы и управления персоналом в Университете Гогенгайма (Hohenheim), заведующий кафедрой. Директор Центра интеллектуальных систем управления персоналом (CIHRS). Исследования фокусируются на цифровизации работы, ИИ в управлении персоналом, цифровом благополучии.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Профессор крупного немецкого университета, руководит исследовательским центром. Публикуется в академических журналах (Group Decision and Negotiation, др.). Следов в русскоязычной деловой среде или широкой узнаваемости среди практиков не найдено.</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>0000-0003-1375-6059</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>https://digital-work.uni-hohenheim.de/henner-gimpel</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи; подтверждён страницей работодателя https://digital-work.uni-hohenheim.de/henner-gimpel</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_09_digital_facilitation_of_group_work_to_gain_predictable</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>api.openalex.org/works/https://doi.org/10.1007/s10726-023-09856-8; поиск 'Henner Gimpel University Hohenheim'; проверка страницы работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>wohl_m</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Moritz Wöhl</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Moritz Wöhl|Мориц Вёль</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>0000-0002-4994-1938</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Научный сотрудник Information Management in Mechanical Engineering (IMA), факультет машиностроения RWTH Aachen University. Исследования сосредоточены на цифровой фасилитации групповой работы и управлении проектами.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Позиция в RWTH Aachen проверяема, публикации в академических журналах (Group Decision and Negotiation, Springer). Следов присутствия в деловой среде не найдено: нет публикаций в деловых медиа, книг, выступлений на корпоративных конференциях.</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>0000-0002-4994-1938</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>https://www.ima.rwth-aachen.de/cms/IMA/Das-Institut/Mitarbeiter/~sezfi/Moritz-Woehl/</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.1007/s10726-023-09856-8; описание со страницы автора на сайте RWTH Aachen University</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_09_digital_facilitation_of_group_work_to_gain_predictable</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>openalex api works doi; moritz wöhl rwth aachen; moritz wöhl digital facilitation; moritz wöhl hbr forbes; moritz wöhl conference speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>graf-drasch_v</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Valerie Graf-Drasch</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Valerie Graf-Drasch</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>0000-0002-4734-7657</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Исследователь в области информационных систем, University of Bayreuth. Работает над темами цифровой фасилитации, краудсорсинга и блокчейн-технологий в бизнес-процессах.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Исследователь с проверяемой позицией в университете, публикации в академических журналах (Group Decision and Negotiation, Electronic Markets). Публичных следов в русскоязычной или англоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>0000-0002-4734-7657</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>https://www.fim.uni-bayreuth.de/de/team/index.php?id=1201</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI статьи https://api.openalex.org/works/https://doi.org/10.1007/s10726-023-09856-8; профиль подтверждён страницей University of Bayreuth</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_09_digital_facilitation_of_group_work_to_gain_predictable</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>openalex api doi:10.1007/s10726-023-09856-8; valerie graf-drasch orcid; valerie graf-drasch university bayreuth</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>suharnomo</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Suharnomo</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Suharnomo</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?user=8cKHx8YAAAAJ</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>профиль_платформы</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Профессор факультета экономики и бизнеса Университета Диponегоро (Индонезия), специализируется на управлении человеческими ресурсами и организационном поведении. Публикуется в журналах по менеджменту.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Профессор индонезийского университета, публикации в академических журналах по менеджменту. Позиция проверяема, следов в русскоязычной деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdikbud.go.id/authors/profile/6004043</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Google Scholar profile https://scholar.google.com/citations?user=8cKHx8YAAAAJ, SINTA (Science and Technology Index Indonesia) profile https://sinta.kemdikbud.go.id/authors/profile/6004043</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Фокус на главном, долгосрочное планирование_02_Gaps_Empowering_Leadership</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Suharnomo UMSurabaya; Suharnomo Diponegoro University; Suharnomo empowering leadership; Suharnomo ORCID</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>djastuti_i</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Indi Djastuti</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Indi Djastuti|И. Джастути</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>0000-0002-8494-0124</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Lecturer, Department of Management, Universitas Muhammadiyah Surabaya</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Преподаватель кафедры менеджмента факультета экономики и бизнеса Университета Мухаммадия Сурабая (Индонезия). Исследует организационное поведение, лидерство и управление персоналом, публикуется в международных журналах по менеджменту.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Исследователь регионального университета в Индонезии. Публикации в академических журналах, следов присутствия в русскоязычной или международной деловой среде не обнаружено. Имя не узнаваемо для корпоративной аудитории.</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>0000-0002-8494-0124</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/authid/detail.uri?authorId=57211495349</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>ORCID указан в метаданных публикаций на Scopus; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Фокус на главном, долгосрочное планирование_02_Gaps_Empowering_Leadership, Фокус на главном, долгосрочное планирование_02_Gaps_Empowering_Leadership, Фокус на главном, долгосрочное планирование_02_Gaps_Empowering_Leadership</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Indi Djastuti UMSurabaya; Indi Djastuti ORCID; Indi Djastuti empowering leadership; Indi Djastuti Universitas Muhammadiyah Surabaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>zierock_b</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Benjamin Zierock</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Benjamin Zierock</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://www.srh-heidelberg.de/en/university/about-us/organisation/people/benjamin-zierock/</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SRH University Heidelberg</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Профессор School of Applied Psychology в SRH University Heidelberg. Исследовательские интересы: цифровизация, организационное обучение, управление изменениями, OKR-методология. Публикуется по темам инноваций и agile-управления проектами.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Профессор немецкого университета, публикации в академических изданиях по OKR и управлению проектами. Деловых медиа, переводов книг, выступлений на корпоративных конференциях или собственной аудитории среди практиков не найдено.</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>https://www.srh-heidelberg.de/en/university/about-us/organisation/people/benjamin-zierock/</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Фокус на главном, долгосрочное планирование_03_team_centric_innovation_the_role_of_objectives_and_key, Фокус на главном, долгосрочное планирование_03_team_centric_innovation_the_role_of_objectives_and_key</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>OpenAlex API по DOI 10.54941/ahfe1004717; поиск 'Benjamin Zierock SRH University Heidelberg'; сайт srh-heidelberg.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>blatz_m</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Matthias Blatz</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Matthias Blatz|Маттиас Блатц</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://heidelberg-it.management/team</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>консультант Heidelberg IT Management</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Консультант Heidelberg IT Management GmbH &amp; Co. KG. Специализируется на цифровой трансформации, управлении проектами и внедрении agile-методологий в организациях.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Публикация в материалах конференции AHFE, работа в консалтинге. Публичных следов в деловых медиа, книг, выступлений на крупных конференциях не найдено.</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>https://heidelberg-it.management/team — профиль на сайте работодателя</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Фокус на главном, долгосрочное планирование_03_team_centric_innovation_the_role_of_objectives_and_key, Фокус на главном, долгосрочное планирование_03_team_centric_innovation_the_role_of_objectives_and_key</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>openalex.org/works/doi:10.54941/ahfe1004717; heidelberg-it.management matthias blatz; matthias blatz orcid; matthias blatz linkedin</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>karcher_k</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Kris Karcher</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Kris Karcher</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>0000-0002-4863-3074</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Applied AI Corporation Limited</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Р4</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Автор статей в академических сборниках по управлению проектами. Следов публичности в деловой среде (книги, колонки, конференции, кейсы) не найдено.</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>0000-0002-4863-3074</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>ORCID из метаданных OpenAlex по DOI 10.54941/ahfe1004717; запись orcid.org недоступна</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>ждёт описания</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Фокус на главном, долгосрочное планирование_03_team_centric_innovation_the_role_of_objectives_and_key, Фокус на главном, долгосрочное планирование_03_team_centric_innovation_the_role_of_objectives_and_key</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>openalex works doi:10.54941/ahfe1004717; Kris Karcher Applied AI Corporation; Kris Karcher OKR project management; appliedai.co.uk team</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>lahmer_s</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Stefanie Lahmer</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Stefanie Lahmer</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://www.modul.ac.at/staff/stefanie-lahmer/</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>страница_у_работодателя</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>человек</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Научный сотрудник MODUL University Vienna, специализируется на групповой динамике и цифровой фасилитации. Автор исследований в области управления конфликтами и организационного поведения.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Р3</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Научный сотрудник университета, публикации в специализированных академических журналах. Позиция проверяема, публичных следов в русскоязычной или широкой деловой среде не найдено.</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>0000-0002-6219-394X</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>ORCID: 0000-0002-6219-394X из метаданных OpenAlex по DOI статьи</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>https://www.modul.ac.at/staff/stefanie-lahmer/</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>подтверждён</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Управление конфликтами_09_digital_facilitation_of_group_work_to_gain_predictable</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>OpenAlex API по DOI 10.1007/s10726-023-09856-8; страница статьи у издателя Springer; MODUL University Vienna staff page; Stefanie Lahmer MODUL University</t>
         </is>
       </c>
     </row>
